--- a/JP1/21_ドキュメント/【Win2016対応】JP1_移行手順書.xlsx
+++ b/JP1/21_ドキュメント/【Win2016対応】JP1_移行手順書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y-tosa\Box\2026_WindowsServer2016対応\DrSum ETL JP1（ＤＨＩ大阪）_WindowsServer2016対応\2_JP1\21_ドキュメント\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tosa_git\proj_DHI_G-foot\JP1\21_ドキュメント\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35A23CD-7E6C-4E85-AA98-279054355194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3174C98E-09E4-47E7-93DF-D608A8EDCE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A9FC5FBD-E884-4C8C-83B8-D15E0B2515A2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{A9FC5FBD-E884-4C8C-83B8-D15E0B2515A2}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="4" r:id="rId1"/>
@@ -141,7 +141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="835">
   <si>
     <t>実行環境</t>
     <rPh sb="0" eb="2">
@@ -4729,6 +4729,9 @@
       <t>カイメ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキップ（本ケースでは実施不要）</t>
   </si>
 </sst>
 </file>
@@ -4969,7 +4972,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFBFBFBF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5195,7 +5198,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5385,16 +5388,16 @@
     <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5408,6 +5411,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -5436,6 +5445,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -5445,31 +5469,16 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5499,20 +5508,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5853,7 +5880,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="7">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="2">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
   <wetp:taskpane dockstate="right" visibility="0" width="287" row="0">
@@ -5896,12 +5923,12 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="B2:P41"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="2" width="3.625" customWidth="1"/>
+    <col min="1" max="2" width="3.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" s="11" customFormat="1" ht="25.5">
+    <row r="2" spans="2:7" s="11" customFormat="1" ht="26.4">
       <c r="B2" s="10" t="s">
         <v>62</v>
       </c>
@@ -5942,24 +5969,24 @@
       </c>
     </row>
     <row r="12" spans="2:7">
-      <c r="D12" s="66" t="s">
+      <c r="D12" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="66"/>
-      <c r="F12" s="64" t="s">
+      <c r="E12" s="72"/>
+      <c r="F12" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="64"/>
+      <c r="G12" s="66"/>
     </row>
     <row r="13" spans="2:7">
-      <c r="D13" s="66" t="s">
+      <c r="D13" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="66"/>
-      <c r="F13" s="64" t="s">
+      <c r="E13" s="72"/>
+      <c r="F13" s="66" t="s">
         <v>697</v>
       </c>
-      <c r="G13" s="64"/>
+      <c r="G13" s="66"/>
     </row>
     <row r="16" spans="2:7">
       <c r="B16" s="15" t="s">
@@ -5992,99 +6019,99 @@
       <c r="P18" s="65"/>
     </row>
     <row r="19" spans="2:16">
-      <c r="D19" s="64" t="s">
+      <c r="D19" s="66" t="s">
         <v>609</v>
       </c>
-      <c r="E19" s="64"/>
-      <c r="F19" s="64"/>
-      <c r="G19" s="64" t="s">
+      <c r="E19" s="66"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="66" t="s">
         <v>610</v>
       </c>
-      <c r="H19" s="64"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="64"/>
-      <c r="K19" s="64"/>
-      <c r="L19" s="64"/>
-      <c r="M19" s="64"/>
-      <c r="N19" s="64"/>
-      <c r="O19" s="64"/>
-      <c r="P19" s="64"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="66"/>
+      <c r="K19" s="66"/>
+      <c r="L19" s="66"/>
+      <c r="M19" s="66"/>
+      <c r="N19" s="66"/>
+      <c r="O19" s="66"/>
+      <c r="P19" s="66"/>
     </row>
     <row r="20" spans="2:16">
-      <c r="D20" s="64" t="s">
+      <c r="D20" s="66" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="64"/>
-      <c r="F20" s="64"/>
-      <c r="G20" s="64" t="s">
+      <c r="E20" s="66"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="66" t="s">
         <v>73</v>
       </c>
-      <c r="H20" s="64"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="64"/>
-      <c r="K20" s="64"/>
-      <c r="L20" s="64"/>
-      <c r="M20" s="64"/>
-      <c r="N20" s="64"/>
-      <c r="O20" s="64"/>
-      <c r="P20" s="64"/>
+      <c r="H20" s="66"/>
+      <c r="I20" s="66"/>
+      <c r="J20" s="66"/>
+      <c r="K20" s="66"/>
+      <c r="L20" s="66"/>
+      <c r="M20" s="66"/>
+      <c r="N20" s="66"/>
+      <c r="O20" s="66"/>
+      <c r="P20" s="66"/>
     </row>
     <row r="21" spans="2:16">
-      <c r="D21" s="64" t="s">
+      <c r="D21" s="66" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="64" t="s">
+      <c r="E21" s="66"/>
+      <c r="F21" s="66"/>
+      <c r="G21" s="66" t="s">
         <v>74</v>
       </c>
-      <c r="H21" s="64"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="64"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="64"/>
-      <c r="M21" s="64"/>
-      <c r="N21" s="64"/>
-      <c r="O21" s="64"/>
-      <c r="P21" s="64"/>
+      <c r="H21" s="66"/>
+      <c r="I21" s="66"/>
+      <c r="J21" s="66"/>
+      <c r="K21" s="66"/>
+      <c r="L21" s="66"/>
+      <c r="M21" s="66"/>
+      <c r="N21" s="66"/>
+      <c r="O21" s="66"/>
+      <c r="P21" s="66"/>
     </row>
     <row r="22" spans="2:16">
-      <c r="D22" s="64" t="s">
+      <c r="D22" s="66" t="s">
         <v>805</v>
       </c>
-      <c r="E22" s="64"/>
-      <c r="F22" s="64"/>
-      <c r="G22" s="64" t="s">
+      <c r="E22" s="66"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="66" t="s">
         <v>765</v>
       </c>
-      <c r="H22" s="64"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="64"/>
-      <c r="K22" s="64"/>
-      <c r="L22" s="64"/>
-      <c r="M22" s="64"/>
-      <c r="N22" s="64"/>
-      <c r="O22" s="64"/>
-      <c r="P22" s="64"/>
+      <c r="H22" s="66"/>
+      <c r="I22" s="66"/>
+      <c r="J22" s="66"/>
+      <c r="K22" s="66"/>
+      <c r="L22" s="66"/>
+      <c r="M22" s="66"/>
+      <c r="N22" s="66"/>
+      <c r="O22" s="66"/>
+      <c r="P22" s="66"/>
     </row>
     <row r="23" spans="2:16">
-      <c r="D23" s="63" t="s">
+      <c r="D23" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="63"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="63" t="s">
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71" t="s">
         <v>766</v>
       </c>
-      <c r="H23" s="63"/>
-      <c r="I23" s="64"/>
-      <c r="J23" s="64"/>
-      <c r="K23" s="64"/>
-      <c r="L23" s="64"/>
-      <c r="M23" s="64"/>
-      <c r="N23" s="64"/>
-      <c r="O23" s="64"/>
-      <c r="P23" s="64"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="66"/>
+      <c r="J23" s="66"/>
+      <c r="K23" s="66"/>
+      <c r="L23" s="66"/>
+      <c r="M23" s="66"/>
+      <c r="N23" s="66"/>
+      <c r="O23" s="66"/>
+      <c r="P23" s="66"/>
     </row>
     <row r="24" spans="2:16">
       <c r="D24" s="59" t="s">
@@ -6367,6 +6394,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="G23:P23"/>
+    <mergeCell ref="G18:P18"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:P20"/>
+    <mergeCell ref="G21:P21"/>
+    <mergeCell ref="G22:P22"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="D18:F18"/>
     <mergeCell ref="E29:P29"/>
     <mergeCell ref="D19:F19"/>
     <mergeCell ref="G19:P19"/>
@@ -6383,19 +6423,6 @@
     <mergeCell ref="E32:P32"/>
     <mergeCell ref="E31:P31"/>
     <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G23:P23"/>
-    <mergeCell ref="G18:P18"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:P20"/>
-    <mergeCell ref="G21:P21"/>
-    <mergeCell ref="G22:P22"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6405,11 +6432,11 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD4B2DBF-7FC0-486D-9990-C1E40D7B1EF2}">
   <dimension ref="B2:Q37"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="3.625" style="14" customWidth="1"/>
+    <col min="1" max="1" width="3.59765625" style="14" customWidth="1"/>
     <col min="2" max="5" width="9" style="14"/>
-    <col min="6" max="6" width="82.75" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="82.69921875" style="14" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="14"/>
   </cols>
   <sheetData>
@@ -6429,49 +6456,49 @@
       <c r="F2" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="87" t="s">
+      <c r="G2" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="87"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="87"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="87"/>
-      <c r="N2" s="87"/>
-      <c r="O2" s="87"/>
-      <c r="P2" s="87"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="86"/>
+      <c r="M2" s="86"/>
+      <c r="N2" s="86"/>
+      <c r="O2" s="86"/>
+      <c r="P2" s="86"/>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="89" t="s">
+      <c r="B3" s="82" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="80"/>
-      <c r="D3" s="83" t="s">
+      <c r="C3" s="87"/>
+      <c r="D3" s="92" t="s">
         <v>125</v>
       </c>
-      <c r="E3" s="85">
+      <c r="E3" s="90">
         <v>1</v>
       </c>
       <c r="F3" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="86"/>
-      <c r="M3" s="86"/>
-      <c r="N3" s="86"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="91"/>
+      <c r="L3" s="91"/>
+      <c r="M3" s="91"/>
+      <c r="N3" s="91"/>
+      <c r="O3" s="91"/>
+      <c r="P3" s="91"/>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="89"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="80"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="87"/>
       <c r="F4" s="70"/>
       <c r="G4" s="70"/>
       <c r="H4" s="70"/>
@@ -6485,16 +6512,16 @@
       <c r="P4" s="70"/>
     </row>
     <row r="5" spans="2:16">
-      <c r="B5" s="90" t="s">
+      <c r="B5" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="80" t="s">
+      <c r="C5" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="81" t="s">
+      <c r="D5" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="E5" s="80">
+      <c r="E5" s="87">
         <v>2</v>
       </c>
       <c r="F5" s="70" t="s">
@@ -6514,10 +6541,10 @@
       <c r="P5" s="70"/>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="90"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="80"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="87"/>
       <c r="F6" s="70"/>
       <c r="G6" s="70"/>
       <c r="H6" s="70"/>
@@ -6531,22 +6558,22 @@
       <c r="P6" s="70"/>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="90" t="s">
+      <c r="B7" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="80" t="s">
+      <c r="C7" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="81" t="s">
+      <c r="D7" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="E7" s="80">
+      <c r="E7" s="87">
         <v>3</v>
       </c>
       <c r="F7" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="G7" s="88" t="s">
+      <c r="G7" s="84" t="s">
         <v>80</v>
       </c>
       <c r="H7" s="70"/>
@@ -6560,10 +6587,10 @@
       <c r="P7" s="70"/>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="90"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="80"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="89"/>
+      <c r="E8" s="87"/>
       <c r="F8" s="70"/>
       <c r="G8" s="70"/>
       <c r="H8" s="70"/>
@@ -6577,16 +6604,16 @@
       <c r="P8" s="70"/>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="91" t="s">
+      <c r="B9" s="85" t="s">
         <v>87</v>
       </c>
-      <c r="C9" s="80" t="s">
+      <c r="C9" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="D9" s="81" t="s">
+      <c r="D9" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="E9" s="80">
+      <c r="E9" s="87">
         <v>4</v>
       </c>
       <c r="F9" s="70" t="s">
@@ -6604,10 +6631,10 @@
       <c r="P9" s="70"/>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="91"/>
-      <c r="C10" s="80"/>
-      <c r="D10" s="82"/>
-      <c r="E10" s="80"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="89"/>
+      <c r="E10" s="87"/>
       <c r="F10" s="70"/>
       <c r="G10" s="70"/>
       <c r="H10" s="70"/>
@@ -6621,16 +6648,16 @@
       <c r="P10" s="70"/>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="90" t="s">
+      <c r="B11" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="80" t="s">
+      <c r="C11" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="81" t="s">
+      <c r="D11" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="E11" s="80">
+      <c r="E11" s="87">
         <v>5</v>
       </c>
       <c r="F11" s="70" t="s">
@@ -6648,10 +6675,10 @@
       <c r="P11" s="70"/>
     </row>
     <row r="12" spans="2:16">
-      <c r="B12" s="90"/>
-      <c r="C12" s="80"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="80"/>
+      <c r="B12" s="83"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="89"/>
+      <c r="E12" s="87"/>
       <c r="F12" s="70"/>
       <c r="G12" s="70"/>
       <c r="H12" s="70"/>
@@ -6665,16 +6692,16 @@
       <c r="P12" s="70"/>
     </row>
     <row r="13" spans="2:16">
-      <c r="B13" s="90" t="s">
+      <c r="B13" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="80" t="s">
+      <c r="C13" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="D13" s="81" t="s">
+      <c r="D13" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="E13" s="80">
+      <c r="E13" s="87">
         <v>6</v>
       </c>
       <c r="F13" s="70" t="s">
@@ -6692,10 +6719,10 @@
       <c r="P13" s="70"/>
     </row>
     <row r="14" spans="2:16">
-      <c r="B14" s="90"/>
-      <c r="C14" s="80"/>
-      <c r="D14" s="82"/>
-      <c r="E14" s="80"/>
+      <c r="B14" s="83"/>
+      <c r="C14" s="87"/>
+      <c r="D14" s="89"/>
+      <c r="E14" s="87"/>
       <c r="F14" s="70"/>
       <c r="G14" s="70"/>
       <c r="H14" s="70"/>
@@ -6709,16 +6736,16 @@
       <c r="P14" s="70"/>
     </row>
     <row r="15" spans="2:16">
-      <c r="B15" s="90" t="s">
+      <c r="B15" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="80" t="s">
+      <c r="C15" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="D15" s="81" t="s">
+      <c r="D15" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="E15" s="80">
+      <c r="E15" s="87">
         <v>7</v>
       </c>
       <c r="F15" s="70" t="s">
@@ -6738,10 +6765,10 @@
       <c r="P15" s="70"/>
     </row>
     <row r="16" spans="2:16">
-      <c r="B16" s="90"/>
-      <c r="C16" s="80"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="80"/>
+      <c r="B16" s="83"/>
+      <c r="C16" s="87"/>
+      <c r="D16" s="89"/>
+      <c r="E16" s="87"/>
       <c r="F16" s="70"/>
       <c r="G16" s="70"/>
       <c r="H16" s="70"/>
@@ -6755,16 +6782,16 @@
       <c r="P16" s="70"/>
     </row>
     <row r="17" spans="2:17">
-      <c r="B17" s="90" t="s">
+      <c r="B17" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="80" t="s">
+      <c r="C17" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="D17" s="81" t="s">
+      <c r="D17" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="E17" s="80">
+      <c r="E17" s="87">
         <v>8</v>
       </c>
       <c r="F17" s="70" t="s">
@@ -6784,10 +6811,10 @@
       <c r="P17" s="70"/>
     </row>
     <row r="18" spans="2:17">
-      <c r="B18" s="90"/>
-      <c r="C18" s="80"/>
-      <c r="D18" s="82"/>
-      <c r="E18" s="80"/>
+      <c r="B18" s="83"/>
+      <c r="C18" s="87"/>
+      <c r="D18" s="89"/>
+      <c r="E18" s="87"/>
       <c r="F18" s="70"/>
       <c r="G18" s="70"/>
       <c r="H18" s="70"/>
@@ -6801,19 +6828,19 @@
       <c r="P18" s="70"/>
     </row>
     <row r="19" spans="2:17">
-      <c r="B19" s="89" t="s">
+      <c r="B19" s="82" t="s">
         <v>85</v>
       </c>
-      <c r="C19" s="80" t="s">
+      <c r="C19" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="81" t="s">
+      <c r="D19" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="E19" s="80">
+      <c r="E19" s="87">
         <v>9</v>
       </c>
-      <c r="F19" s="88" t="s">
+      <c r="F19" s="84" t="s">
         <v>637</v>
       </c>
       <c r="G19" s="70" t="s">
@@ -6833,10 +6860,10 @@
       </c>
     </row>
     <row r="20" spans="2:17">
-      <c r="B20" s="89"/>
-      <c r="C20" s="80"/>
-      <c r="D20" s="82"/>
-      <c r="E20" s="80"/>
+      <c r="B20" s="82"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="89"/>
+      <c r="E20" s="87"/>
       <c r="F20" s="70"/>
       <c r="G20" s="70"/>
       <c r="H20" s="70"/>
@@ -6850,107 +6877,107 @@
       <c r="P20" s="70"/>
     </row>
     <row r="21" spans="2:17" ht="18.75" customHeight="1">
-      <c r="B21" s="89" t="s">
+      <c r="B21" s="82" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="80"/>
-      <c r="D21" s="83" t="s">
+      <c r="C21" s="87"/>
+      <c r="D21" s="92" t="s">
         <v>125</v>
       </c>
-      <c r="E21" s="80">
+      <c r="E21" s="87">
         <v>10</v>
       </c>
-      <c r="F21" s="88" t="s">
+      <c r="F21" s="84" t="s">
         <v>83</v>
       </c>
-      <c r="G21" s="88" t="s">
+      <c r="G21" s="84" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="88"/>
-      <c r="I21" s="88"/>
-      <c r="J21" s="88"/>
-      <c r="K21" s="88"/>
-      <c r="L21" s="88"/>
-      <c r="M21" s="88"/>
-      <c r="N21" s="88"/>
-      <c r="O21" s="88"/>
-      <c r="P21" s="88"/>
+      <c r="H21" s="84"/>
+      <c r="I21" s="84"/>
+      <c r="J21" s="84"/>
+      <c r="K21" s="84"/>
+      <c r="L21" s="84"/>
+      <c r="M21" s="84"/>
+      <c r="N21" s="84"/>
+      <c r="O21" s="84"/>
+      <c r="P21" s="84"/>
     </row>
     <row r="22" spans="2:17">
-      <c r="B22" s="89"/>
-      <c r="C22" s="80"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="80"/>
-      <c r="F22" s="88"/>
-      <c r="G22" s="88"/>
-      <c r="H22" s="88"/>
-      <c r="I22" s="88"/>
-      <c r="J22" s="88"/>
-      <c r="K22" s="88"/>
-      <c r="L22" s="88"/>
-      <c r="M22" s="88"/>
-      <c r="N22" s="88"/>
-      <c r="O22" s="88"/>
-      <c r="P22" s="88"/>
+      <c r="B22" s="82"/>
+      <c r="C22" s="87"/>
+      <c r="D22" s="93"/>
+      <c r="E22" s="87"/>
+      <c r="F22" s="84"/>
+      <c r="G22" s="84"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="84"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="84"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="84"/>
+      <c r="N22" s="84"/>
+      <c r="O22" s="84"/>
+      <c r="P22" s="84"/>
     </row>
     <row r="23" spans="2:17" ht="18.75" customHeight="1">
-      <c r="B23" s="89" t="s">
+      <c r="B23" s="82" t="s">
         <v>85</v>
       </c>
-      <c r="C23" s="80" t="s">
+      <c r="C23" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="D23" s="81" t="s">
+      <c r="D23" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="E23" s="80">
+      <c r="E23" s="87">
         <v>11</v>
       </c>
       <c r="F23" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="88" t="s">
+      <c r="G23" s="84" t="s">
         <v>82</v>
       </c>
-      <c r="H23" s="88"/>
-      <c r="I23" s="88"/>
-      <c r="J23" s="88"/>
-      <c r="K23" s="88"/>
-      <c r="L23" s="88"/>
-      <c r="M23" s="88"/>
-      <c r="N23" s="88"/>
-      <c r="O23" s="88"/>
-      <c r="P23" s="88"/>
+      <c r="H23" s="84"/>
+      <c r="I23" s="84"/>
+      <c r="J23" s="84"/>
+      <c r="K23" s="84"/>
+      <c r="L23" s="84"/>
+      <c r="M23" s="84"/>
+      <c r="N23" s="84"/>
+      <c r="O23" s="84"/>
+      <c r="P23" s="84"/>
       <c r="Q23" s="14" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="24" spans="2:17">
-      <c r="B24" s="89"/>
-      <c r="C24" s="80"/>
-      <c r="D24" s="82"/>
-      <c r="E24" s="80"/>
+      <c r="B24" s="82"/>
+      <c r="C24" s="87"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="87"/>
       <c r="F24" s="70"/>
-      <c r="G24" s="88"/>
-      <c r="H24" s="88"/>
-      <c r="I24" s="88"/>
-      <c r="J24" s="88"/>
-      <c r="K24" s="88"/>
-      <c r="L24" s="88"/>
-      <c r="M24" s="88"/>
-      <c r="N24" s="88"/>
-      <c r="O24" s="88"/>
-      <c r="P24" s="88"/>
+      <c r="G24" s="84"/>
+      <c r="H24" s="84"/>
+      <c r="I24" s="84"/>
+      <c r="J24" s="84"/>
+      <c r="K24" s="84"/>
+      <c r="L24" s="84"/>
+      <c r="M24" s="84"/>
+      <c r="N24" s="84"/>
+      <c r="O24" s="84"/>
+      <c r="P24" s="84"/>
     </row>
     <row r="25" spans="2:17">
-      <c r="B25" s="89" t="s">
+      <c r="B25" s="82" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="80"/>
-      <c r="D25" s="81" t="s">
+      <c r="C25" s="87"/>
+      <c r="D25" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="E25" s="80">
+      <c r="E25" s="87">
         <v>12</v>
       </c>
       <c r="F25" s="70" t="s">
@@ -6973,10 +7000,10 @@
       </c>
     </row>
     <row r="26" spans="2:17">
-      <c r="B26" s="89"/>
-      <c r="C26" s="80"/>
-      <c r="D26" s="82"/>
-      <c r="E26" s="80"/>
+      <c r="B26" s="82"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="89"/>
+      <c r="E26" s="87"/>
       <c r="F26" s="70"/>
       <c r="G26" s="70"/>
       <c r="H26" s="70"/>
@@ -6990,17 +7017,17 @@
       <c r="P26" s="70"/>
     </row>
     <row r="27" spans="2:17">
-      <c r="B27" s="90" t="s">
+      <c r="B27" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="C27" s="80"/>
-      <c r="D27" s="83" t="s">
+      <c r="C27" s="87"/>
+      <c r="D27" s="92" t="s">
         <v>125</v>
       </c>
-      <c r="E27" s="80">
+      <c r="E27" s="87">
         <v>13</v>
       </c>
-      <c r="F27" s="88" t="s">
+      <c r="F27" s="84" t="s">
         <v>88</v>
       </c>
       <c r="G27" s="70"/>
@@ -7015,10 +7042,10 @@
       <c r="P27" s="70"/>
     </row>
     <row r="28" spans="2:17">
-      <c r="B28" s="90"/>
-      <c r="C28" s="80"/>
-      <c r="D28" s="84"/>
-      <c r="E28" s="80"/>
+      <c r="B28" s="83"/>
+      <c r="C28" s="87"/>
+      <c r="D28" s="93"/>
+      <c r="E28" s="87"/>
       <c r="F28" s="70"/>
       <c r="G28" s="70"/>
       <c r="H28" s="70"/>
@@ -7032,14 +7059,14 @@
       <c r="P28" s="70"/>
     </row>
     <row r="29" spans="2:17">
-      <c r="B29" s="89" t="s">
+      <c r="B29" s="82" t="s">
         <v>85</v>
       </c>
-      <c r="C29" s="80"/>
-      <c r="D29" s="83" t="s">
+      <c r="C29" s="87"/>
+      <c r="D29" s="92" t="s">
         <v>125</v>
       </c>
-      <c r="E29" s="80">
+      <c r="E29" s="87">
         <v>14</v>
       </c>
       <c r="F29" s="70" t="s">
@@ -7057,10 +7084,10 @@
       <c r="P29" s="70"/>
     </row>
     <row r="30" spans="2:17">
-      <c r="B30" s="89"/>
-      <c r="C30" s="80"/>
-      <c r="D30" s="84"/>
-      <c r="E30" s="80"/>
+      <c r="B30" s="82"/>
+      <c r="C30" s="87"/>
+      <c r="D30" s="93"/>
+      <c r="E30" s="87"/>
       <c r="F30" s="70"/>
       <c r="G30" s="70"/>
       <c r="H30" s="70"/>
@@ -7113,11 +7140,70 @@
     </row>
   </sheetData>
   <mergeCells count="85">
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="G3:P4"/>
+    <mergeCell ref="G5:P6"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="G11:P12"/>
+    <mergeCell ref="G13:P14"/>
+    <mergeCell ref="G15:P16"/>
+    <mergeCell ref="G17:P18"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="G27:P28"/>
+    <mergeCell ref="G29:P30"/>
+    <mergeCell ref="G2:P2"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="G19:P20"/>
+    <mergeCell ref="G21:P22"/>
+    <mergeCell ref="G23:P24"/>
+    <mergeCell ref="G25:P26"/>
+    <mergeCell ref="G7:P8"/>
+    <mergeCell ref="G9:P10"/>
     <mergeCell ref="F21:F22"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="B5:B6"/>
@@ -7134,70 +7220,11 @@
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G27:P28"/>
-    <mergeCell ref="G29:P30"/>
-    <mergeCell ref="G2:P2"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="G19:P20"/>
-    <mergeCell ref="G21:P22"/>
-    <mergeCell ref="G23:P24"/>
-    <mergeCell ref="G25:P26"/>
-    <mergeCell ref="G7:P8"/>
-    <mergeCell ref="G9:P10"/>
-    <mergeCell ref="G13:P14"/>
-    <mergeCell ref="G15:P16"/>
-    <mergeCell ref="G17:P18"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="G3:P4"/>
-    <mergeCell ref="G5:P6"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="G11:P12"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B29:B30"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7211,43 +7238,43 @@
     <tabColor theme="1"/>
   </sheetPr>
   <dimension ref="A2:Q8"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="6.625" style="14" customWidth="1"/>
+    <col min="1" max="1" width="6.59765625" style="14" customWidth="1"/>
     <col min="2" max="16" width="9" style="14" customWidth="1"/>
     <col min="17" max="16384" width="9" style="14"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" s="13" customFormat="1" ht="18">
+    <row r="2" spans="1:17" s="13" customFormat="1">
       <c r="B2" s="13" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="7" customFormat="1" ht="15.75">
+    <row r="4" spans="1:17" s="7" customFormat="1" ht="15">
       <c r="A4" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="95" t="s">
+      <c r="B4" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="95" t="s">
+      <c r="C4" s="98"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="96"/>
-      <c r="H4" s="96"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="95" t="s">
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="96"/>
-      <c r="L4" s="96"/>
-      <c r="M4" s="96"/>
-      <c r="N4" s="96"/>
-      <c r="O4" s="96"/>
-      <c r="P4" s="97"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="98"/>
+      <c r="P4" s="99"/>
       <c r="Q4" s="6" t="s">
         <v>2</v>
       </c>
@@ -7262,48 +7289,48 @@
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
-      <c r="F5" s="98" t="s">
+      <c r="F5" s="100" t="s">
         <v>90</v>
       </c>
-      <c r="G5" s="99"/>
-      <c r="H5" s="99"/>
-      <c r="I5" s="100"/>
-      <c r="J5" s="92" t="s">
+      <c r="G5" s="101"/>
+      <c r="H5" s="101"/>
+      <c r="I5" s="102"/>
+      <c r="J5" s="94" t="s">
         <v>94</v>
       </c>
-      <c r="K5" s="93"/>
-      <c r="L5" s="93"/>
-      <c r="M5" s="93"/>
-      <c r="N5" s="93"/>
-      <c r="O5" s="93"/>
-      <c r="P5" s="94"/>
+      <c r="K5" s="95"/>
+      <c r="L5" s="95"/>
+      <c r="M5" s="95"/>
+      <c r="N5" s="95"/>
+      <c r="O5" s="95"/>
+      <c r="P5" s="96"/>
       <c r="Q5" s="18"/>
     </row>
     <row r="6" spans="1:17" ht="165.75" customHeight="1">
       <c r="A6" s="19">
         <v>2</v>
       </c>
-      <c r="B6" s="92" t="s">
+      <c r="B6" s="94" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="93"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="94"/>
-      <c r="F6" s="92" t="s">
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="96"/>
+      <c r="F6" s="94" t="s">
         <v>93</v>
       </c>
-      <c r="G6" s="93"/>
-      <c r="H6" s="93"/>
-      <c r="I6" s="94"/>
-      <c r="J6" s="92" t="s">
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="96"/>
+      <c r="J6" s="94" t="s">
         <v>608</v>
       </c>
-      <c r="K6" s="93"/>
-      <c r="L6" s="93"/>
-      <c r="M6" s="93"/>
-      <c r="N6" s="93"/>
-      <c r="O6" s="93"/>
-      <c r="P6" s="94"/>
+      <c r="K6" s="95"/>
+      <c r="L6" s="95"/>
+      <c r="M6" s="95"/>
+      <c r="N6" s="95"/>
+      <c r="O6" s="95"/>
+      <c r="P6" s="96"/>
       <c r="Q6" s="19"/>
     </row>
     <row r="8" spans="1:17">
@@ -7333,16 +7360,16 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="B2:E8"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="2" width="3.625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="29.625" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="3.59765625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="29.59765625" style="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="76.5" style="14" customWidth="1"/>
-    <col min="5" max="5" width="33.875" style="14" customWidth="1"/>
+    <col min="5" max="5" width="33.8984375" style="14" customWidth="1"/>
     <col min="6" max="16384" width="9" style="14"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" s="13" customFormat="1" ht="25.5">
+    <row r="2" spans="2:5" s="13" customFormat="1" ht="26.4">
       <c r="B2" s="12" t="s">
         <v>63</v>
       </c>
@@ -7361,7 +7388,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="93.75">
+    <row r="5" spans="2:5" ht="90">
       <c r="B5" s="19">
         <v>1</v>
       </c>
@@ -7385,7 +7412,7 @@
       </c>
       <c r="E6" s="19"/>
     </row>
-    <row r="7" spans="2:5" ht="168.75">
+    <row r="7" spans="2:5" ht="162">
       <c r="B7" s="19">
         <v>3</v>
       </c>
@@ -7416,23 +7443,23 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:L24"/>
-  <sheetFormatPr defaultColWidth="4" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="4" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="6.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.59765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.19921875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="37" style="1" customWidth="1"/>
-    <col min="6" max="6" width="53.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="61.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="33.75" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.75" style="1" customWidth="1"/>
-    <col min="11" max="11" width="16.75" style="1" customWidth="1"/>
-    <col min="12" max="12" width="35.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="53.59765625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="61.8984375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="33.69921875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.8984375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.69921875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.69921875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="35.59765625" style="1" customWidth="1"/>
     <col min="13" max="16384" width="4" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="19.5">
+    <row r="1" spans="1:12" ht="18.600000000000001">
       <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
@@ -7442,12 +7469,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="19.5">
+    <row r="2" spans="1:12" ht="18.600000000000001">
       <c r="A2" s="28"/>
       <c r="B2" s="28"/>
       <c r="E2" s="7"/>
     </row>
-    <row r="3" spans="1:12" ht="19.5">
+    <row r="3" spans="1:12" ht="18.600000000000001">
       <c r="A3" s="28"/>
       <c r="B3" s="28"/>
       <c r="D3" s="7" t="s">
@@ -7455,7 +7482,7 @@
       </c>
       <c r="E3" s="7"/>
     </row>
-    <row r="4" spans="1:12" ht="19.5">
+    <row r="4" spans="1:12" ht="18.600000000000001">
       <c r="A4" s="28"/>
       <c r="B4" s="28"/>
       <c r="D4" s="20"/>
@@ -7463,11 +7490,13 @@
         <v>768</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="19.5">
+    <row r="5" spans="1:12" ht="18.600000000000001">
       <c r="A5" s="28"/>
       <c r="B5" s="28"/>
       <c r="D5" s="22"/>
-      <c r="E5" s="7"/>
+      <c r="E5" s="7" t="s">
+        <v>834</v>
+      </c>
     </row>
     <row r="6" spans="1:12">
       <c r="E6" s="52" t="s">
@@ -7512,7 +7541,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="31.5">
+    <row r="8" spans="1:12" ht="30">
       <c r="A8" s="47">
         <v>1</v>
       </c>
@@ -7603,10 +7632,10 @@
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="1:12" ht="147" customHeight="1">
-      <c r="A11" s="71">
+      <c r="A11" s="73">
         <v>4</v>
       </c>
-      <c r="B11" s="102" t="s">
+      <c r="B11" s="64" t="s">
         <v>105</v>
       </c>
       <c r="C11" s="47" t="s">
@@ -7635,97 +7664,97 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="270" customHeight="1">
-      <c r="A12" s="72"/>
-      <c r="B12" s="103" t="s">
+      <c r="A12" s="74"/>
+      <c r="B12" s="110" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="47" t="s">
+      <c r="C12" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="111" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="61" t="s">
+      <c r="E12" s="112" t="s">
         <v>772</v>
       </c>
-      <c r="F12" s="49" t="s">
+      <c r="F12" s="113" t="s">
         <v>713</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="113" t="s">
         <v>98</v>
       </c>
-      <c r="H12" s="49" t="s">
+      <c r="H12" s="113" t="s">
         <v>714</v>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
     </row>
     <row r="13" spans="1:12" ht="222" customHeight="1">
-      <c r="A13" s="71">
+      <c r="A13" s="103">
         <v>5</v>
       </c>
-      <c r="B13" s="48" t="s">
+      <c r="B13" s="104" t="s">
         <v>112</v>
       </c>
       <c r="C13" s="105" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="106" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="60" t="s">
+      <c r="E13" s="107" t="s">
         <v>773</v>
       </c>
-      <c r="F13" s="60" t="s">
+      <c r="F13" s="107" t="s">
         <v>774</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="106" t="s">
         <v>816</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="106" t="s">
         <v>38</v>
       </c>
-      <c r="I13" s="104" t="s">
+      <c r="I13" s="106" t="s">
         <v>833</v>
       </c>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="3" t="s">
+      <c r="J13" s="105"/>
+      <c r="K13" s="105"/>
+      <c r="L13" s="106" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="154.5" customHeight="1">
-      <c r="A14" s="72"/>
-      <c r="B14" s="48" t="s">
+      <c r="A14" s="108"/>
+      <c r="B14" s="104" t="s">
         <v>113</v>
       </c>
-      <c r="C14" s="47" t="s">
+      <c r="C14" s="105" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="109" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="60" t="s">
+      <c r="E14" s="107" t="s">
         <v>775</v>
       </c>
-      <c r="F14" s="60" t="s">
+      <c r="F14" s="107" t="s">
         <v>776</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="106" t="s">
         <v>98</v>
       </c>
-      <c r="H14" s="60" t="s">
+      <c r="H14" s="107" t="s">
         <v>777</v>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
+      <c r="I14" s="105"/>
+      <c r="J14" s="105"/>
+      <c r="K14" s="105"/>
+      <c r="L14" s="105"/>
     </row>
     <row r="15" spans="1:12" ht="219.75" customHeight="1">
-      <c r="A15" s="71">
+      <c r="A15" s="73">
         <v>6</v>
       </c>
       <c r="B15" s="48" t="s">
@@ -7757,32 +7786,32 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="154.5" customHeight="1">
-      <c r="A16" s="72"/>
-      <c r="B16" s="48" t="s">
+      <c r="A16" s="74"/>
+      <c r="B16" s="110" t="s">
         <v>642</v>
       </c>
-      <c r="C16" s="47" t="s">
+      <c r="C16" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="E16" s="60" t="s">
+      <c r="E16" s="112" t="s">
         <v>779</v>
       </c>
-      <c r="F16" s="60" t="s">
+      <c r="F16" s="112" t="s">
         <v>776</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="113" t="s">
         <v>98</v>
       </c>
-      <c r="H16" s="60" t="s">
+      <c r="H16" s="112" t="s">
         <v>780</v>
       </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
     </row>
     <row r="17" spans="1:12" ht="201.75" customHeight="1">
       <c r="A17" s="47">
@@ -7838,7 +7867,7 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="B1:J22"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="2:10">
       <c r="H1" s="44" t="s">
@@ -7875,7 +7904,7 @@
       </c>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="101" t="s">
+      <c r="B9" s="63" t="s">
         <v>810</v>
       </c>
     </row>
@@ -7885,7 +7914,7 @@
       </c>
     </row>
     <row r="12" spans="2:10">
-      <c r="B12" s="101" t="s">
+      <c r="B12" s="63" t="s">
         <v>811</v>
       </c>
     </row>
@@ -7895,7 +7924,7 @@
       </c>
     </row>
     <row r="15" spans="2:10">
-      <c r="B15" s="101" t="s">
+      <c r="B15" s="63" t="s">
         <v>812</v>
       </c>
     </row>
@@ -7905,7 +7934,7 @@
       </c>
     </row>
     <row r="18" spans="2:2">
-      <c r="B18" s="101" t="s">
+      <c r="B18" s="63" t="s">
         <v>813</v>
       </c>
     </row>
@@ -7936,23 +7965,23 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultColWidth="4" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="4" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="6.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.59765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.09765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="37" style="1" customWidth="1"/>
-    <col min="6" max="6" width="41.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="67.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="33.75" style="1" customWidth="1"/>
-    <col min="9" max="9" width="29.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="16.875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="29.875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="35.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="41.8984375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="67.69921875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="33.69921875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="29.8984375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.8984375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="29.8984375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="35.59765625" style="1" customWidth="1"/>
     <col min="13" max="16384" width="4" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="19.5">
+    <row r="1" spans="1:12" ht="18.600000000000001">
       <c r="A1" s="5" t="s">
         <v>16</v>
       </c>
@@ -7963,7 +7992,7 @@
       </c>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:12" ht="19.5">
+    <row r="2" spans="1:12" ht="18.600000000000001">
       <c r="A2" s="28"/>
       <c r="B2" s="28"/>
       <c r="D2" s="7" t="s">
@@ -7971,7 +8000,7 @@
       </c>
       <c r="E2" s="7"/>
     </row>
-    <row r="3" spans="1:12" ht="19.5">
+    <row r="3" spans="1:12" ht="18.600000000000001">
       <c r="A3" s="28"/>
       <c r="B3" s="28"/>
       <c r="D3" s="20"/>
@@ -7979,7 +8008,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="19.5">
+    <row r="4" spans="1:12" ht="18.600000000000001">
       <c r="A4" s="28"/>
       <c r="B4" s="28"/>
       <c r="D4" s="22"/>
@@ -7987,7 +8016,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="19.5">
+    <row r="5" spans="1:12" ht="18.600000000000001">
       <c r="A5" s="28"/>
       <c r="B5" s="28"/>
       <c r="D5" s="29"/>
@@ -8036,7 +8065,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="31.5">
+    <row r="8" spans="1:12" ht="30">
       <c r="A8" s="47">
         <v>1</v>
       </c>
@@ -8097,7 +8126,7 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="1:12" ht="140.1" customHeight="1">
-      <c r="A10" s="71">
+      <c r="A10" s="73">
         <v>3</v>
       </c>
       <c r="B10" s="50" t="s">
@@ -8106,10 +8135,10 @@
       <c r="C10" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="78" t="s">
+      <c r="D10" s="80" t="s">
         <v>698</v>
       </c>
-      <c r="E10" s="73" t="s">
+      <c r="E10" s="75" t="s">
         <v>817</v>
       </c>
       <c r="F10" s="3" t="s">
@@ -8129,15 +8158,15 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="87.75" customHeight="1">
-      <c r="A11" s="77"/>
+      <c r="A11" s="79"/>
       <c r="B11" s="50" t="s">
         <v>102</v>
       </c>
       <c r="C11" s="51" t="s">
         <v>653</v>
       </c>
-      <c r="D11" s="79"/>
-      <c r="E11" s="74"/>
+      <c r="D11" s="81"/>
+      <c r="E11" s="76"/>
       <c r="F11" s="3" t="s">
         <v>31</v>
       </c>
@@ -8153,7 +8182,7 @@
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" ht="103.5" customHeight="1">
-      <c r="A12" s="72"/>
+      <c r="A12" s="74"/>
       <c r="B12" s="50" t="s">
         <v>109</v>
       </c>
@@ -8181,7 +8210,7 @@
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" ht="140.1" customHeight="1">
-      <c r="A13" s="71">
+      <c r="A13" s="73">
         <v>4</v>
       </c>
       <c r="B13" s="48" t="s">
@@ -8190,10 +8219,10 @@
       <c r="C13" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="78" t="s">
+      <c r="D13" s="80" t="s">
         <v>698</v>
       </c>
-      <c r="E13" s="75" t="s">
+      <c r="E13" s="77" t="s">
         <v>781</v>
       </c>
       <c r="F13" s="3" t="s">
@@ -8213,15 +8242,15 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="70.5" customHeight="1">
-      <c r="A14" s="77"/>
+      <c r="A14" s="79"/>
       <c r="B14" s="48" t="s">
         <v>110</v>
       </c>
       <c r="C14" s="51" t="s">
         <v>654</v>
       </c>
-      <c r="D14" s="79"/>
-      <c r="E14" s="76"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="78"/>
       <c r="F14" s="3" t="s">
         <v>31</v>
       </c>
@@ -8237,7 +8266,7 @@
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12" ht="93" customHeight="1">
-      <c r="A15" s="72"/>
+      <c r="A15" s="74"/>
       <c r="B15" s="48" t="s">
         <v>111</v>
       </c>
@@ -8265,7 +8294,7 @@
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" ht="195" customHeight="1">
-      <c r="A16" s="71">
+      <c r="A16" s="73">
         <v>5</v>
       </c>
       <c r="B16" s="48" t="s">
@@ -8274,10 +8303,10 @@
       <c r="C16" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="78" t="s">
+      <c r="D16" s="80" t="s">
         <v>698</v>
       </c>
-      <c r="E16" s="75" t="s">
+      <c r="E16" s="77" t="s">
         <v>786</v>
       </c>
       <c r="F16" s="3" t="s">
@@ -8297,15 +8326,15 @@
       </c>
     </row>
     <row r="17" spans="1:12" ht="70.5" customHeight="1">
-      <c r="A17" s="77"/>
+      <c r="A17" s="79"/>
       <c r="B17" s="48" t="s">
         <v>113</v>
       </c>
       <c r="C17" s="51" t="s">
         <v>655</v>
       </c>
-      <c r="D17" s="79"/>
-      <c r="E17" s="76"/>
+      <c r="D17" s="81"/>
+      <c r="E17" s="78"/>
       <c r="F17" s="3" t="s">
         <v>31</v>
       </c>
@@ -8321,7 +8350,7 @@
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" ht="93" customHeight="1">
-      <c r="A18" s="72"/>
+      <c r="A18" s="74"/>
       <c r="B18" s="48" t="s">
         <v>114</v>
       </c>
@@ -8442,9 +8471,9 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="B1:E21"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="76.625" customWidth="1"/>
+    <col min="2" max="2" width="76.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5">
@@ -8543,23 +8572,23 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:L507"/>
-  <sheetFormatPr defaultColWidth="4" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="4" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="6.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.59765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.19921875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="37" style="1" customWidth="1"/>
-    <col min="6" max="6" width="44.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="61.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="33.75" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.75" style="1" customWidth="1"/>
-    <col min="11" max="11" width="16.75" style="1" customWidth="1"/>
-    <col min="12" max="12" width="35.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="44.8984375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="61.8984375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="33.69921875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.8984375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.69921875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.69921875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="35.59765625" style="1" customWidth="1"/>
     <col min="13" max="16384" width="4" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="19.5">
+    <row r="1" spans="1:12" ht="18.600000000000001">
       <c r="A1" s="5" t="s">
         <v>632</v>
       </c>
@@ -8822,7 +8851,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="18.75">
+    <row r="14" spans="1:12" ht="18">
       <c r="E14"/>
       <c r="F14"/>
       <c r="G14"/>
@@ -8832,7 +8861,7 @@
       <c r="K14"/>
       <c r="L14"/>
     </row>
-    <row r="15" spans="1:12" ht="18.75">
+    <row r="15" spans="1:12" ht="18">
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15"/>
@@ -8842,7 +8871,7 @@
       <c r="K15"/>
       <c r="L15"/>
     </row>
-    <row r="16" spans="1:12" ht="18.75">
+    <row r="16" spans="1:12" ht="18">
       <c r="E16"/>
       <c r="F16"/>
       <c r="G16"/>
@@ -8852,7 +8881,7 @@
       <c r="K16"/>
       <c r="L16"/>
     </row>
-    <row r="17" spans="5:12" ht="18.75">
+    <row r="17" spans="5:12" ht="18">
       <c r="E17"/>
       <c r="F17"/>
       <c r="G17"/>
@@ -8862,7 +8891,7 @@
       <c r="K17"/>
       <c r="L17"/>
     </row>
-    <row r="18" spans="5:12" ht="18.75">
+    <row r="18" spans="5:12" ht="18">
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18"/>
@@ -8882,7 +8911,7 @@
       <c r="K19"/>
       <c r="L19"/>
     </row>
-    <row r="20" spans="5:12" ht="18.75">
+    <row r="20" spans="5:12" ht="18">
       <c r="E20"/>
       <c r="F20"/>
       <c r="G20"/>
@@ -8892,7 +8921,7 @@
       <c r="K20"/>
       <c r="L20"/>
     </row>
-    <row r="21" spans="5:12" ht="18.75">
+    <row r="21" spans="5:12" ht="18">
       <c r="E21"/>
       <c r="F21"/>
       <c r="G21"/>
@@ -8902,7 +8931,7 @@
       <c r="K21"/>
       <c r="L21"/>
     </row>
-    <row r="22" spans="5:12" ht="18.75">
+    <row r="22" spans="5:12" ht="18">
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22"/>
@@ -8912,7 +8941,7 @@
       <c r="K22"/>
       <c r="L22"/>
     </row>
-    <row r="23" spans="5:12" ht="18.75">
+    <row r="23" spans="5:12" ht="18">
       <c r="E23"/>
       <c r="F23"/>
       <c r="G23"/>
@@ -8922,7 +8951,7 @@
       <c r="K23"/>
       <c r="L23"/>
     </row>
-    <row r="24" spans="5:12" ht="18.75">
+    <row r="24" spans="5:12" ht="18">
       <c r="E24"/>
       <c r="F24"/>
       <c r="G24"/>
@@ -8932,7 +8961,7 @@
       <c r="K24"/>
       <c r="L24"/>
     </row>
-    <row r="25" spans="5:12" ht="18.75">
+    <row r="25" spans="5:12" ht="18">
       <c r="E25"/>
       <c r="F25"/>
       <c r="G25"/>
@@ -8942,7 +8971,7 @@
       <c r="K25"/>
       <c r="L25"/>
     </row>
-    <row r="26" spans="5:12" ht="18.75">
+    <row r="26" spans="5:12" ht="18">
       <c r="E26"/>
       <c r="F26"/>
       <c r="G26"/>
@@ -8952,7 +8981,7 @@
       <c r="K26"/>
       <c r="L26"/>
     </row>
-    <row r="27" spans="5:12" ht="18.75">
+    <row r="27" spans="5:12" ht="18">
       <c r="E27"/>
       <c r="F27"/>
       <c r="G27"/>
@@ -8962,7 +8991,7 @@
       <c r="K27"/>
       <c r="L27"/>
     </row>
-    <row r="28" spans="5:12" ht="18.75">
+    <row r="28" spans="5:12" ht="18">
       <c r="E28"/>
       <c r="F28"/>
       <c r="G28"/>
@@ -8972,7 +9001,7 @@
       <c r="K28"/>
       <c r="L28"/>
     </row>
-    <row r="29" spans="5:12" ht="18.75">
+    <row r="29" spans="5:12" ht="18">
       <c r="E29"/>
       <c r="F29"/>
       <c r="G29"/>
@@ -8982,7 +9011,7 @@
       <c r="K29"/>
       <c r="L29"/>
     </row>
-    <row r="30" spans="5:12" ht="18.75">
+    <row r="30" spans="5:12" ht="18">
       <c r="E30"/>
       <c r="F30"/>
       <c r="G30"/>
@@ -8992,7 +9021,7 @@
       <c r="K30"/>
       <c r="L30"/>
     </row>
-    <row r="31" spans="5:12" ht="18.75">
+    <row r="31" spans="5:12" ht="18">
       <c r="E31"/>
       <c r="F31"/>
       <c r="G31"/>
@@ -9002,7 +9031,7 @@
       <c r="K31"/>
       <c r="L31"/>
     </row>
-    <row r="32" spans="5:12" ht="18.75">
+    <row r="32" spans="5:12" ht="18">
       <c r="E32"/>
       <c r="F32"/>
       <c r="G32"/>
@@ -9012,7 +9041,7 @@
       <c r="K32"/>
       <c r="L32"/>
     </row>
-    <row r="33" spans="5:12" ht="18.75">
+    <row r="33" spans="5:12" ht="18">
       <c r="E33"/>
       <c r="F33"/>
       <c r="G33"/>
@@ -9022,7 +9051,7 @@
       <c r="K33"/>
       <c r="L33"/>
     </row>
-    <row r="34" spans="5:12" ht="18.75">
+    <row r="34" spans="5:12" ht="18">
       <c r="E34"/>
       <c r="F34"/>
       <c r="G34"/>
@@ -9032,7 +9061,7 @@
       <c r="K34"/>
       <c r="L34"/>
     </row>
-    <row r="35" spans="5:12" ht="18.75">
+    <row r="35" spans="5:12" ht="18">
       <c r="E35"/>
       <c r="F35"/>
       <c r="G35"/>
@@ -9042,7 +9071,7 @@
       <c r="K35"/>
       <c r="L35"/>
     </row>
-    <row r="36" spans="5:12" ht="18.75">
+    <row r="36" spans="5:12" ht="18">
       <c r="E36"/>
       <c r="F36"/>
       <c r="G36"/>
@@ -9052,7 +9081,7 @@
       <c r="K36"/>
       <c r="L36"/>
     </row>
-    <row r="37" spans="5:12" ht="18.75">
+    <row r="37" spans="5:12" ht="18">
       <c r="E37"/>
       <c r="F37"/>
       <c r="G37"/>
@@ -9062,7 +9091,7 @@
       <c r="K37"/>
       <c r="L37"/>
     </row>
-    <row r="38" spans="5:12" ht="18.75">
+    <row r="38" spans="5:12" ht="18">
       <c r="E38"/>
       <c r="F38"/>
       <c r="G38"/>
@@ -9072,7 +9101,7 @@
       <c r="K38"/>
       <c r="L38"/>
     </row>
-    <row r="39" spans="5:12" ht="18.75">
+    <row r="39" spans="5:12" ht="18">
       <c r="E39"/>
       <c r="F39"/>
       <c r="G39"/>
@@ -9082,7 +9111,7 @@
       <c r="K39"/>
       <c r="L39"/>
     </row>
-    <row r="40" spans="5:12" ht="18.75">
+    <row r="40" spans="5:12" ht="18">
       <c r="E40"/>
       <c r="F40"/>
       <c r="G40"/>
@@ -9092,7 +9121,7 @@
       <c r="K40"/>
       <c r="L40"/>
     </row>
-    <row r="41" spans="5:12" ht="18.75">
+    <row r="41" spans="5:12" ht="18">
       <c r="E41"/>
       <c r="F41"/>
       <c r="G41"/>
@@ -9102,7 +9131,7 @@
       <c r="K41"/>
       <c r="L41"/>
     </row>
-    <row r="42" spans="5:12" ht="18.75">
+    <row r="42" spans="5:12" ht="18">
       <c r="E42"/>
       <c r="F42"/>
       <c r="G42"/>
@@ -9112,7 +9141,7 @@
       <c r="K42"/>
       <c r="L42"/>
     </row>
-    <row r="43" spans="5:12" ht="18.75">
+    <row r="43" spans="5:12" ht="18">
       <c r="E43"/>
       <c r="F43"/>
       <c r="G43"/>
@@ -9122,7 +9151,7 @@
       <c r="K43"/>
       <c r="L43"/>
     </row>
-    <row r="44" spans="5:12" ht="18.75">
+    <row r="44" spans="5:12" ht="18">
       <c r="E44"/>
       <c r="F44"/>
       <c r="G44"/>
@@ -9132,7 +9161,7 @@
       <c r="K44"/>
       <c r="L44"/>
     </row>
-    <row r="45" spans="5:12" ht="18.75">
+    <row r="45" spans="5:12" ht="18">
       <c r="E45"/>
       <c r="F45"/>
       <c r="G45"/>
@@ -9142,7 +9171,7 @@
       <c r="K45"/>
       <c r="L45"/>
     </row>
-    <row r="46" spans="5:12" ht="18.75">
+    <row r="46" spans="5:12" ht="18">
       <c r="E46"/>
       <c r="F46"/>
       <c r="G46"/>
@@ -9152,7 +9181,7 @@
       <c r="K46"/>
       <c r="L46"/>
     </row>
-    <row r="47" spans="5:12" ht="18.75">
+    <row r="47" spans="5:12" ht="18">
       <c r="E47"/>
       <c r="F47"/>
       <c r="G47"/>
@@ -9162,7 +9191,7 @@
       <c r="K47"/>
       <c r="L47"/>
     </row>
-    <row r="48" spans="5:12" ht="18.75">
+    <row r="48" spans="5:12" ht="18">
       <c r="E48"/>
       <c r="F48"/>
       <c r="G48"/>
@@ -9172,7 +9201,7 @@
       <c r="K48"/>
       <c r="L48"/>
     </row>
-    <row r="49" spans="5:12" ht="18.75">
+    <row r="49" spans="5:12" ht="18">
       <c r="E49"/>
       <c r="F49"/>
       <c r="G49"/>
@@ -9182,7 +9211,7 @@
       <c r="K49"/>
       <c r="L49"/>
     </row>
-    <row r="50" spans="5:12" ht="18.75">
+    <row r="50" spans="5:12" ht="18">
       <c r="E50"/>
       <c r="F50"/>
       <c r="G50"/>
@@ -9192,7 +9221,7 @@
       <c r="K50"/>
       <c r="L50"/>
     </row>
-    <row r="51" spans="5:12" ht="18.75">
+    <row r="51" spans="5:12" ht="18">
       <c r="E51"/>
       <c r="F51"/>
       <c r="G51"/>
@@ -9202,7 +9231,7 @@
       <c r="K51"/>
       <c r="L51"/>
     </row>
-    <row r="52" spans="5:12" ht="18.75">
+    <row r="52" spans="5:12" ht="18">
       <c r="E52"/>
       <c r="F52"/>
       <c r="G52"/>
@@ -9212,7 +9241,7 @@
       <c r="K52"/>
       <c r="L52"/>
     </row>
-    <row r="53" spans="5:12" ht="18.75">
+    <row r="53" spans="5:12" ht="18">
       <c r="E53"/>
       <c r="F53"/>
       <c r="G53"/>
@@ -9222,7 +9251,7 @@
       <c r="K53"/>
       <c r="L53"/>
     </row>
-    <row r="54" spans="5:12" ht="18.75">
+    <row r="54" spans="5:12" ht="18">
       <c r="E54"/>
       <c r="F54"/>
       <c r="G54"/>
@@ -9232,7 +9261,7 @@
       <c r="K54"/>
       <c r="L54"/>
     </row>
-    <row r="55" spans="5:12" ht="18.75">
+    <row r="55" spans="5:12" ht="18">
       <c r="E55"/>
       <c r="F55"/>
       <c r="G55"/>
@@ -9242,7 +9271,7 @@
       <c r="K55"/>
       <c r="L55"/>
     </row>
-    <row r="56" spans="5:12" ht="18.75">
+    <row r="56" spans="5:12" ht="18">
       <c r="E56"/>
       <c r="F56"/>
       <c r="G56"/>
@@ -9252,7 +9281,7 @@
       <c r="K56"/>
       <c r="L56"/>
     </row>
-    <row r="57" spans="5:12" ht="18.75">
+    <row r="57" spans="5:12" ht="18">
       <c r="E57"/>
       <c r="F57"/>
       <c r="G57"/>
@@ -9262,7 +9291,7 @@
       <c r="K57"/>
       <c r="L57"/>
     </row>
-    <row r="58" spans="5:12" ht="18.75">
+    <row r="58" spans="5:12" ht="18">
       <c r="E58"/>
       <c r="F58"/>
       <c r="G58"/>
@@ -9272,7 +9301,7 @@
       <c r="K58"/>
       <c r="L58"/>
     </row>
-    <row r="59" spans="5:12" ht="18.75">
+    <row r="59" spans="5:12" ht="18">
       <c r="E59"/>
       <c r="F59"/>
       <c r="G59"/>
@@ -9282,7 +9311,7 @@
       <c r="K59"/>
       <c r="L59"/>
     </row>
-    <row r="60" spans="5:12" ht="18.75">
+    <row r="60" spans="5:12" ht="18">
       <c r="E60"/>
       <c r="F60"/>
       <c r="G60"/>
@@ -9292,7 +9321,7 @@
       <c r="K60"/>
       <c r="L60"/>
     </row>
-    <row r="61" spans="5:12" ht="18.75">
+    <row r="61" spans="5:12" ht="18">
       <c r="E61"/>
       <c r="F61"/>
       <c r="G61"/>
@@ -9302,7 +9331,7 @@
       <c r="K61"/>
       <c r="L61"/>
     </row>
-    <row r="62" spans="5:12" ht="18.75">
+    <row r="62" spans="5:12" ht="18">
       <c r="E62"/>
       <c r="F62"/>
       <c r="G62"/>
@@ -9312,7 +9341,7 @@
       <c r="K62"/>
       <c r="L62"/>
     </row>
-    <row r="63" spans="5:12" ht="18.75">
+    <row r="63" spans="5:12" ht="18">
       <c r="E63"/>
       <c r="F63"/>
       <c r="G63"/>
@@ -9322,7 +9351,7 @@
       <c r="K63"/>
       <c r="L63"/>
     </row>
-    <row r="64" spans="5:12" ht="18.75">
+    <row r="64" spans="5:12" ht="18">
       <c r="E64"/>
       <c r="F64"/>
       <c r="G64"/>
@@ -9332,7 +9361,7 @@
       <c r="K64"/>
       <c r="L64"/>
     </row>
-    <row r="65" spans="5:12" ht="18.75">
+    <row r="65" spans="5:12" ht="18">
       <c r="E65"/>
       <c r="F65"/>
       <c r="G65"/>
@@ -9342,7 +9371,7 @@
       <c r="K65"/>
       <c r="L65"/>
     </row>
-    <row r="66" spans="5:12" ht="18.75">
+    <row r="66" spans="5:12" ht="18">
       <c r="E66"/>
       <c r="F66"/>
       <c r="G66"/>
@@ -9352,7 +9381,7 @@
       <c r="K66"/>
       <c r="L66"/>
     </row>
-    <row r="67" spans="5:12" ht="18.75">
+    <row r="67" spans="5:12" ht="18">
       <c r="E67"/>
       <c r="F67"/>
       <c r="G67"/>
@@ -9362,7 +9391,7 @@
       <c r="K67"/>
       <c r="L67"/>
     </row>
-    <row r="68" spans="5:12" ht="18.75">
+    <row r="68" spans="5:12" ht="18">
       <c r="E68"/>
       <c r="F68"/>
       <c r="G68"/>
@@ -9372,7 +9401,7 @@
       <c r="K68"/>
       <c r="L68"/>
     </row>
-    <row r="69" spans="5:12" ht="18.75">
+    <row r="69" spans="5:12" ht="18">
       <c r="E69"/>
       <c r="F69"/>
       <c r="G69"/>
@@ -9382,7 +9411,7 @@
       <c r="K69"/>
       <c r="L69"/>
     </row>
-    <row r="70" spans="5:12" ht="18.75">
+    <row r="70" spans="5:12" ht="18">
       <c r="E70"/>
       <c r="F70"/>
       <c r="G70"/>
@@ -9392,7 +9421,7 @@
       <c r="K70"/>
       <c r="L70"/>
     </row>
-    <row r="71" spans="5:12" ht="18.75">
+    <row r="71" spans="5:12" ht="18">
       <c r="E71"/>
       <c r="F71"/>
       <c r="G71"/>
@@ -9402,7 +9431,7 @@
       <c r="K71"/>
       <c r="L71"/>
     </row>
-    <row r="72" spans="5:12" ht="18.75">
+    <row r="72" spans="5:12" ht="18">
       <c r="E72"/>
       <c r="F72"/>
       <c r="G72"/>
@@ -9412,7 +9441,7 @@
       <c r="K72"/>
       <c r="L72"/>
     </row>
-    <row r="73" spans="5:12" ht="18.75">
+    <row r="73" spans="5:12" ht="18">
       <c r="E73"/>
       <c r="F73"/>
       <c r="G73"/>
@@ -9422,7 +9451,7 @@
       <c r="K73"/>
       <c r="L73"/>
     </row>
-    <row r="74" spans="5:12" ht="18.75">
+    <row r="74" spans="5:12" ht="18">
       <c r="E74"/>
       <c r="F74"/>
       <c r="G74"/>
@@ -9432,7 +9461,7 @@
       <c r="K74"/>
       <c r="L74"/>
     </row>
-    <row r="75" spans="5:12" ht="18.75">
+    <row r="75" spans="5:12" ht="18">
       <c r="E75"/>
       <c r="F75"/>
       <c r="G75"/>
@@ -9442,7 +9471,7 @@
       <c r="K75"/>
       <c r="L75"/>
     </row>
-    <row r="76" spans="5:12" ht="18.75">
+    <row r="76" spans="5:12" ht="18">
       <c r="E76"/>
       <c r="F76"/>
       <c r="G76"/>
@@ -9452,7 +9481,7 @@
       <c r="K76"/>
       <c r="L76"/>
     </row>
-    <row r="77" spans="5:12" ht="18.75">
+    <row r="77" spans="5:12" ht="18">
       <c r="E77"/>
       <c r="F77"/>
       <c r="G77"/>
@@ -9462,7 +9491,7 @@
       <c r="K77"/>
       <c r="L77"/>
     </row>
-    <row r="78" spans="5:12" ht="18.75">
+    <row r="78" spans="5:12" ht="18">
       <c r="E78"/>
       <c r="F78"/>
       <c r="G78"/>
@@ -9472,7 +9501,7 @@
       <c r="K78"/>
       <c r="L78"/>
     </row>
-    <row r="79" spans="5:12" ht="18.75">
+    <row r="79" spans="5:12" ht="18">
       <c r="E79"/>
       <c r="F79"/>
       <c r="G79"/>
@@ -9482,7 +9511,7 @@
       <c r="K79"/>
       <c r="L79"/>
     </row>
-    <row r="80" spans="5:12" ht="18.75">
+    <row r="80" spans="5:12" ht="18">
       <c r="E80"/>
       <c r="F80"/>
       <c r="G80"/>
@@ -9492,7 +9521,7 @@
       <c r="K80"/>
       <c r="L80"/>
     </row>
-    <row r="81" spans="5:12" ht="18.75">
+    <row r="81" spans="5:12" ht="18">
       <c r="E81"/>
       <c r="F81"/>
       <c r="G81"/>
@@ -9502,7 +9531,7 @@
       <c r="K81"/>
       <c r="L81"/>
     </row>
-    <row r="82" spans="5:12" ht="18.75">
+    <row r="82" spans="5:12" ht="18">
       <c r="E82"/>
       <c r="F82"/>
       <c r="G82"/>
@@ -9512,7 +9541,7 @@
       <c r="K82"/>
       <c r="L82"/>
     </row>
-    <row r="83" spans="5:12" ht="18.75">
+    <row r="83" spans="5:12" ht="18">
       <c r="E83"/>
       <c r="F83"/>
       <c r="G83"/>
@@ -9522,7 +9551,7 @@
       <c r="K83"/>
       <c r="L83"/>
     </row>
-    <row r="84" spans="5:12" ht="18.75">
+    <row r="84" spans="5:12" ht="18">
       <c r="E84"/>
       <c r="F84"/>
       <c r="G84"/>
@@ -9532,7 +9561,7 @@
       <c r="K84"/>
       <c r="L84"/>
     </row>
-    <row r="85" spans="5:12" ht="18.75">
+    <row r="85" spans="5:12" ht="18">
       <c r="E85"/>
       <c r="F85"/>
       <c r="G85"/>
@@ -9542,7 +9571,7 @@
       <c r="K85"/>
       <c r="L85"/>
     </row>
-    <row r="86" spans="5:12" ht="18.75">
+    <row r="86" spans="5:12" ht="18">
       <c r="E86"/>
       <c r="F86"/>
       <c r="G86"/>
@@ -9552,7 +9581,7 @@
       <c r="K86"/>
       <c r="L86"/>
     </row>
-    <row r="87" spans="5:12" ht="18.75">
+    <row r="87" spans="5:12" ht="18">
       <c r="E87"/>
       <c r="F87"/>
       <c r="G87"/>
@@ -9562,7 +9591,7 @@
       <c r="K87"/>
       <c r="L87"/>
     </row>
-    <row r="88" spans="5:12" ht="18.75">
+    <row r="88" spans="5:12" ht="18">
       <c r="E88"/>
       <c r="F88"/>
       <c r="G88"/>
@@ -9572,7 +9601,7 @@
       <c r="K88"/>
       <c r="L88"/>
     </row>
-    <row r="89" spans="5:12" ht="18.75">
+    <row r="89" spans="5:12" ht="18">
       <c r="E89"/>
       <c r="F89"/>
       <c r="G89"/>
@@ -9582,7 +9611,7 @@
       <c r="K89"/>
       <c r="L89"/>
     </row>
-    <row r="90" spans="5:12" ht="18.75">
+    <row r="90" spans="5:12" ht="18">
       <c r="E90"/>
       <c r="F90"/>
       <c r="G90"/>
@@ -9592,7 +9621,7 @@
       <c r="K90"/>
       <c r="L90"/>
     </row>
-    <row r="91" spans="5:12" ht="18.75">
+    <row r="91" spans="5:12" ht="18">
       <c r="E91"/>
       <c r="F91"/>
       <c r="G91"/>
@@ -9602,7 +9631,7 @@
       <c r="K91"/>
       <c r="L91"/>
     </row>
-    <row r="92" spans="5:12" ht="18.75">
+    <row r="92" spans="5:12" ht="18">
       <c r="E92"/>
       <c r="F92"/>
       <c r="G92"/>
@@ -9612,7 +9641,7 @@
       <c r="K92"/>
       <c r="L92"/>
     </row>
-    <row r="93" spans="5:12" ht="18.75">
+    <row r="93" spans="5:12" ht="18">
       <c r="E93"/>
       <c r="F93"/>
       <c r="G93"/>
@@ -9622,7 +9651,7 @@
       <c r="K93"/>
       <c r="L93"/>
     </row>
-    <row r="94" spans="5:12" ht="18.75">
+    <row r="94" spans="5:12" ht="18">
       <c r="E94"/>
       <c r="F94"/>
       <c r="G94"/>
@@ -9632,7 +9661,7 @@
       <c r="K94"/>
       <c r="L94"/>
     </row>
-    <row r="95" spans="5:12" ht="18.75">
+    <row r="95" spans="5:12" ht="18">
       <c r="E95"/>
       <c r="F95"/>
       <c r="G95"/>
@@ -9642,7 +9671,7 @@
       <c r="K95"/>
       <c r="L95"/>
     </row>
-    <row r="96" spans="5:12" ht="18.75">
+    <row r="96" spans="5:12" ht="18">
       <c r="E96"/>
       <c r="F96"/>
       <c r="G96"/>
@@ -9652,7 +9681,7 @@
       <c r="K96"/>
       <c r="L96"/>
     </row>
-    <row r="97" spans="5:12" ht="18.75">
+    <row r="97" spans="5:12" ht="18">
       <c r="E97"/>
       <c r="F97"/>
       <c r="G97"/>
@@ -9662,7 +9691,7 @@
       <c r="K97"/>
       <c r="L97"/>
     </row>
-    <row r="98" spans="5:12" ht="18.75">
+    <row r="98" spans="5:12" ht="18">
       <c r="E98"/>
       <c r="F98"/>
       <c r="G98"/>
@@ -9672,7 +9701,7 @@
       <c r="K98"/>
       <c r="L98"/>
     </row>
-    <row r="99" spans="5:12" ht="18.75">
+    <row r="99" spans="5:12" ht="18">
       <c r="E99"/>
       <c r="F99"/>
       <c r="G99"/>
@@ -9682,7 +9711,7 @@
       <c r="K99"/>
       <c r="L99"/>
     </row>
-    <row r="100" spans="5:12" ht="18.75">
+    <row r="100" spans="5:12" ht="18">
       <c r="E100"/>
       <c r="F100"/>
       <c r="G100"/>
@@ -9692,7 +9721,7 @@
       <c r="K100"/>
       <c r="L100"/>
     </row>
-    <row r="101" spans="5:12" ht="18.75">
+    <row r="101" spans="5:12" ht="18">
       <c r="E101"/>
       <c r="F101"/>
       <c r="G101"/>
@@ -9702,7 +9731,7 @@
       <c r="K101"/>
       <c r="L101"/>
     </row>
-    <row r="102" spans="5:12" ht="18.75">
+    <row r="102" spans="5:12" ht="18">
       <c r="E102"/>
       <c r="F102"/>
       <c r="G102"/>
@@ -9712,7 +9741,7 @@
       <c r="K102"/>
       <c r="L102"/>
     </row>
-    <row r="103" spans="5:12" ht="18.75">
+    <row r="103" spans="5:12" ht="18">
       <c r="E103"/>
       <c r="F103"/>
       <c r="G103"/>
@@ -9722,7 +9751,7 @@
       <c r="K103"/>
       <c r="L103"/>
     </row>
-    <row r="104" spans="5:12" ht="18.75">
+    <row r="104" spans="5:12" ht="18">
       <c r="E104"/>
       <c r="F104"/>
       <c r="G104"/>
@@ -9732,7 +9761,7 @@
       <c r="K104"/>
       <c r="L104"/>
     </row>
-    <row r="105" spans="5:12" ht="18.75">
+    <row r="105" spans="5:12" ht="18">
       <c r="E105"/>
       <c r="F105"/>
       <c r="G105"/>
@@ -9742,7 +9771,7 @@
       <c r="K105"/>
       <c r="L105"/>
     </row>
-    <row r="106" spans="5:12" ht="18.75">
+    <row r="106" spans="5:12" ht="18">
       <c r="E106"/>
       <c r="F106"/>
       <c r="G106"/>
@@ -9752,7 +9781,7 @@
       <c r="K106"/>
       <c r="L106"/>
     </row>
-    <row r="107" spans="5:12" ht="18.75">
+    <row r="107" spans="5:12" ht="18">
       <c r="E107"/>
       <c r="F107"/>
       <c r="G107"/>
@@ -9762,7 +9791,7 @@
       <c r="K107"/>
       <c r="L107"/>
     </row>
-    <row r="108" spans="5:12" ht="18.75">
+    <row r="108" spans="5:12" ht="18">
       <c r="E108"/>
       <c r="F108"/>
       <c r="G108"/>
@@ -9772,7 +9801,7 @@
       <c r="K108"/>
       <c r="L108"/>
     </row>
-    <row r="109" spans="5:12" ht="18.75">
+    <row r="109" spans="5:12" ht="18">
       <c r="E109"/>
       <c r="F109"/>
       <c r="G109"/>
@@ -9782,7 +9811,7 @@
       <c r="K109"/>
       <c r="L109"/>
     </row>
-    <row r="110" spans="5:12" ht="18.75">
+    <row r="110" spans="5:12" ht="18">
       <c r="E110"/>
       <c r="F110"/>
       <c r="G110"/>
@@ -9792,7 +9821,7 @@
       <c r="K110"/>
       <c r="L110"/>
     </row>
-    <row r="111" spans="5:12" ht="18.75">
+    <row r="111" spans="5:12" ht="18">
       <c r="E111"/>
       <c r="F111"/>
       <c r="G111"/>
@@ -9802,7 +9831,7 @@
       <c r="K111"/>
       <c r="L111"/>
     </row>
-    <row r="112" spans="5:12" ht="18.75">
+    <row r="112" spans="5:12" ht="18">
       <c r="E112"/>
       <c r="F112"/>
       <c r="G112"/>
@@ -9812,7 +9841,7 @@
       <c r="K112"/>
       <c r="L112"/>
     </row>
-    <row r="113" spans="5:12" ht="18.75">
+    <row r="113" spans="5:12" ht="18">
       <c r="E113"/>
       <c r="F113"/>
       <c r="G113"/>
@@ -9822,7 +9851,7 @@
       <c r="K113"/>
       <c r="L113"/>
     </row>
-    <row r="114" spans="5:12" ht="18.75">
+    <row r="114" spans="5:12" ht="18">
       <c r="E114"/>
       <c r="F114"/>
       <c r="G114"/>
@@ -9832,7 +9861,7 @@
       <c r="K114"/>
       <c r="L114"/>
     </row>
-    <row r="115" spans="5:12" ht="18.75">
+    <row r="115" spans="5:12" ht="18">
       <c r="E115"/>
       <c r="F115"/>
       <c r="G115"/>
@@ -9842,7 +9871,7 @@
       <c r="K115"/>
       <c r="L115"/>
     </row>
-    <row r="116" spans="5:12" ht="18.75">
+    <row r="116" spans="5:12" ht="18">
       <c r="E116"/>
       <c r="F116"/>
       <c r="G116"/>
@@ -9852,7 +9881,7 @@
       <c r="K116"/>
       <c r="L116"/>
     </row>
-    <row r="117" spans="5:12" ht="18.75">
+    <row r="117" spans="5:12" ht="18">
       <c r="E117"/>
       <c r="F117"/>
       <c r="G117"/>
@@ -9862,7 +9891,7 @@
       <c r="K117"/>
       <c r="L117"/>
     </row>
-    <row r="118" spans="5:12" ht="18.75">
+    <row r="118" spans="5:12" ht="18">
       <c r="E118"/>
       <c r="F118"/>
       <c r="G118"/>
@@ -9872,7 +9901,7 @@
       <c r="K118"/>
       <c r="L118"/>
     </row>
-    <row r="119" spans="5:12" ht="18.75">
+    <row r="119" spans="5:12" ht="18">
       <c r="E119"/>
       <c r="F119"/>
       <c r="G119"/>
@@ -9882,7 +9911,7 @@
       <c r="K119"/>
       <c r="L119"/>
     </row>
-    <row r="120" spans="5:12" ht="18.75">
+    <row r="120" spans="5:12" ht="18">
       <c r="E120"/>
       <c r="F120"/>
       <c r="G120"/>
@@ -9892,7 +9921,7 @@
       <c r="K120"/>
       <c r="L120"/>
     </row>
-    <row r="121" spans="5:12" ht="18.75">
+    <row r="121" spans="5:12" ht="18">
       <c r="E121"/>
       <c r="F121"/>
       <c r="G121"/>
@@ -9902,7 +9931,7 @@
       <c r="K121"/>
       <c r="L121"/>
     </row>
-    <row r="122" spans="5:12" ht="18.75">
+    <row r="122" spans="5:12" ht="18">
       <c r="E122"/>
       <c r="F122"/>
       <c r="G122"/>
@@ -9912,7 +9941,7 @@
       <c r="K122"/>
       <c r="L122"/>
     </row>
-    <row r="123" spans="5:12" ht="18.75">
+    <row r="123" spans="5:12" ht="18">
       <c r="E123"/>
       <c r="F123"/>
       <c r="G123"/>
@@ -9922,7 +9951,7 @@
       <c r="K123"/>
       <c r="L123"/>
     </row>
-    <row r="124" spans="5:12" ht="18.75">
+    <row r="124" spans="5:12" ht="18">
       <c r="E124"/>
       <c r="F124"/>
       <c r="G124"/>
@@ -9932,7 +9961,7 @@
       <c r="K124"/>
       <c r="L124"/>
     </row>
-    <row r="125" spans="5:12" ht="18.75">
+    <row r="125" spans="5:12" ht="18">
       <c r="E125"/>
       <c r="F125"/>
       <c r="G125"/>
@@ -9942,7 +9971,7 @@
       <c r="K125"/>
       <c r="L125"/>
     </row>
-    <row r="126" spans="5:12" ht="18.75">
+    <row r="126" spans="5:12" ht="18">
       <c r="E126"/>
       <c r="F126"/>
       <c r="G126"/>
@@ -9952,7 +9981,7 @@
       <c r="K126"/>
       <c r="L126"/>
     </row>
-    <row r="127" spans="5:12" ht="18.75">
+    <row r="127" spans="5:12" ht="18">
       <c r="E127"/>
       <c r="F127"/>
       <c r="G127"/>
@@ -9962,7 +9991,7 @@
       <c r="K127"/>
       <c r="L127"/>
     </row>
-    <row r="128" spans="5:12" ht="18.75">
+    <row r="128" spans="5:12" ht="18">
       <c r="E128"/>
       <c r="F128"/>
       <c r="G128"/>
@@ -9972,7 +10001,7 @@
       <c r="K128"/>
       <c r="L128"/>
     </row>
-    <row r="129" spans="5:12" ht="18.75">
+    <row r="129" spans="5:12" ht="18">
       <c r="E129"/>
       <c r="F129"/>
       <c r="G129"/>
@@ -9982,7 +10011,7 @@
       <c r="K129"/>
       <c r="L129"/>
     </row>
-    <row r="130" spans="5:12" ht="18.75">
+    <row r="130" spans="5:12" ht="18">
       <c r="E130"/>
       <c r="F130"/>
       <c r="G130"/>
@@ -9992,7 +10021,7 @@
       <c r="K130"/>
       <c r="L130"/>
     </row>
-    <row r="131" spans="5:12" ht="18.75">
+    <row r="131" spans="5:12" ht="18">
       <c r="E131"/>
       <c r="F131"/>
       <c r="G131"/>
@@ -10002,7 +10031,7 @@
       <c r="K131"/>
       <c r="L131"/>
     </row>
-    <row r="132" spans="5:12" ht="18.75">
+    <row r="132" spans="5:12" ht="18">
       <c r="E132"/>
       <c r="F132"/>
       <c r="G132"/>
@@ -10012,7 +10041,7 @@
       <c r="K132"/>
       <c r="L132"/>
     </row>
-    <row r="133" spans="5:12" ht="18.75">
+    <row r="133" spans="5:12" ht="18">
       <c r="E133"/>
       <c r="F133"/>
       <c r="G133"/>
@@ -10022,7 +10051,7 @@
       <c r="K133"/>
       <c r="L133"/>
     </row>
-    <row r="134" spans="5:12" ht="18.75">
+    <row r="134" spans="5:12" ht="18">
       <c r="E134"/>
       <c r="F134"/>
       <c r="G134"/>
@@ -10032,7 +10061,7 @@
       <c r="K134"/>
       <c r="L134"/>
     </row>
-    <row r="135" spans="5:12" ht="18.75">
+    <row r="135" spans="5:12" ht="18">
       <c r="E135"/>
       <c r="F135"/>
       <c r="G135"/>
@@ -10042,7 +10071,7 @@
       <c r="K135"/>
       <c r="L135"/>
     </row>
-    <row r="136" spans="5:12" ht="18.75">
+    <row r="136" spans="5:12" ht="18">
       <c r="E136"/>
       <c r="F136"/>
       <c r="G136"/>
@@ -10052,7 +10081,7 @@
       <c r="K136"/>
       <c r="L136"/>
     </row>
-    <row r="137" spans="5:12" ht="18.75">
+    <row r="137" spans="5:12" ht="18">
       <c r="E137"/>
       <c r="F137"/>
       <c r="G137"/>
@@ -10062,7 +10091,7 @@
       <c r="K137"/>
       <c r="L137"/>
     </row>
-    <row r="138" spans="5:12" ht="18.75">
+    <row r="138" spans="5:12" ht="18">
       <c r="E138"/>
       <c r="F138"/>
       <c r="G138"/>
@@ -10072,7 +10101,7 @@
       <c r="K138"/>
       <c r="L138"/>
     </row>
-    <row r="139" spans="5:12" ht="18.75">
+    <row r="139" spans="5:12" ht="18">
       <c r="E139"/>
       <c r="F139"/>
       <c r="G139"/>
@@ -10082,7 +10111,7 @@
       <c r="K139"/>
       <c r="L139"/>
     </row>
-    <row r="140" spans="5:12" ht="18.75">
+    <row r="140" spans="5:12" ht="18">
       <c r="E140"/>
       <c r="F140"/>
       <c r="G140"/>
@@ -10092,7 +10121,7 @@
       <c r="K140"/>
       <c r="L140"/>
     </row>
-    <row r="141" spans="5:12" ht="18.75">
+    <row r="141" spans="5:12" ht="18">
       <c r="E141"/>
       <c r="F141"/>
       <c r="G141"/>
@@ -10102,7 +10131,7 @@
       <c r="K141"/>
       <c r="L141"/>
     </row>
-    <row r="142" spans="5:12" ht="18.75">
+    <row r="142" spans="5:12" ht="18">
       <c r="E142"/>
       <c r="F142"/>
       <c r="G142"/>
@@ -10112,7 +10141,7 @@
       <c r="K142"/>
       <c r="L142"/>
     </row>
-    <row r="143" spans="5:12" ht="18.75">
+    <row r="143" spans="5:12" ht="18">
       <c r="E143"/>
       <c r="F143"/>
       <c r="G143"/>
@@ -10122,7 +10151,7 @@
       <c r="K143"/>
       <c r="L143"/>
     </row>
-    <row r="144" spans="5:12" ht="18.75">
+    <row r="144" spans="5:12" ht="18">
       <c r="E144"/>
       <c r="F144"/>
       <c r="G144"/>
@@ -10132,7 +10161,7 @@
       <c r="K144"/>
       <c r="L144"/>
     </row>
-    <row r="145" spans="5:12" ht="18.75">
+    <row r="145" spans="5:12" ht="18">
       <c r="E145"/>
       <c r="F145"/>
       <c r="G145"/>
@@ -10142,7 +10171,7 @@
       <c r="K145"/>
       <c r="L145"/>
     </row>
-    <row r="146" spans="5:12" ht="18.75">
+    <row r="146" spans="5:12" ht="18">
       <c r="E146"/>
       <c r="F146"/>
       <c r="G146"/>
@@ -10152,7 +10181,7 @@
       <c r="K146"/>
       <c r="L146"/>
     </row>
-    <row r="147" spans="5:12" ht="18.75">
+    <row r="147" spans="5:12" ht="18">
       <c r="E147"/>
       <c r="F147"/>
       <c r="G147"/>
@@ -10162,7 +10191,7 @@
       <c r="K147"/>
       <c r="L147"/>
     </row>
-    <row r="148" spans="5:12" ht="18.75">
+    <row r="148" spans="5:12" ht="18">
       <c r="E148"/>
       <c r="F148"/>
       <c r="G148"/>
@@ -10172,7 +10201,7 @@
       <c r="K148"/>
       <c r="L148"/>
     </row>
-    <row r="149" spans="5:12" ht="18.75">
+    <row r="149" spans="5:12" ht="18">
       <c r="E149"/>
       <c r="F149"/>
       <c r="G149"/>
@@ -10182,7 +10211,7 @@
       <c r="K149"/>
       <c r="L149"/>
     </row>
-    <row r="150" spans="5:12" ht="18.75">
+    <row r="150" spans="5:12" ht="18">
       <c r="E150"/>
       <c r="F150"/>
       <c r="G150"/>
@@ -10192,7 +10221,7 @@
       <c r="K150"/>
       <c r="L150"/>
     </row>
-    <row r="151" spans="5:12" ht="18.75">
+    <row r="151" spans="5:12" ht="18">
       <c r="E151"/>
       <c r="F151"/>
       <c r="G151"/>
@@ -10202,7 +10231,7 @@
       <c r="K151"/>
       <c r="L151"/>
     </row>
-    <row r="152" spans="5:12" ht="18.75">
+    <row r="152" spans="5:12" ht="18">
       <c r="E152"/>
       <c r="F152"/>
       <c r="G152"/>
@@ -10212,7 +10241,7 @@
       <c r="K152"/>
       <c r="L152"/>
     </row>
-    <row r="153" spans="5:12" ht="18.75">
+    <row r="153" spans="5:12" ht="18">
       <c r="E153"/>
       <c r="F153"/>
       <c r="G153"/>
@@ -10222,7 +10251,7 @@
       <c r="K153"/>
       <c r="L153"/>
     </row>
-    <row r="154" spans="5:12" ht="18.75">
+    <row r="154" spans="5:12" ht="18">
       <c r="E154"/>
       <c r="F154"/>
       <c r="G154"/>
@@ -10232,7 +10261,7 @@
       <c r="K154"/>
       <c r="L154"/>
     </row>
-    <row r="155" spans="5:12" ht="18.75">
+    <row r="155" spans="5:12" ht="18">
       <c r="E155"/>
       <c r="F155"/>
       <c r="G155"/>
@@ -10242,7 +10271,7 @@
       <c r="K155"/>
       <c r="L155"/>
     </row>
-    <row r="156" spans="5:12" ht="18.75">
+    <row r="156" spans="5:12" ht="18">
       <c r="E156"/>
       <c r="F156"/>
       <c r="G156"/>
@@ -10252,7 +10281,7 @@
       <c r="K156"/>
       <c r="L156"/>
     </row>
-    <row r="157" spans="5:12" ht="18.75">
+    <row r="157" spans="5:12" ht="18">
       <c r="E157"/>
       <c r="F157"/>
       <c r="G157"/>
@@ -10262,7 +10291,7 @@
       <c r="K157"/>
       <c r="L157"/>
     </row>
-    <row r="158" spans="5:12" ht="18.75">
+    <row r="158" spans="5:12" ht="18">
       <c r="E158"/>
       <c r="F158"/>
       <c r="G158"/>
@@ -10272,7 +10301,7 @@
       <c r="K158"/>
       <c r="L158"/>
     </row>
-    <row r="159" spans="5:12" ht="18.75">
+    <row r="159" spans="5:12" ht="18">
       <c r="E159"/>
       <c r="F159"/>
       <c r="G159"/>
@@ -10282,7 +10311,7 @@
       <c r="K159"/>
       <c r="L159"/>
     </row>
-    <row r="160" spans="5:12" ht="18.75">
+    <row r="160" spans="5:12" ht="18">
       <c r="E160"/>
       <c r="F160"/>
       <c r="G160"/>
@@ -10292,7 +10321,7 @@
       <c r="K160"/>
       <c r="L160"/>
     </row>
-    <row r="161" spans="5:12" ht="18.75">
+    <row r="161" spans="5:12" ht="18">
       <c r="E161"/>
       <c r="F161"/>
       <c r="G161"/>
@@ -10302,7 +10331,7 @@
       <c r="K161"/>
       <c r="L161"/>
     </row>
-    <row r="162" spans="5:12" ht="18.75">
+    <row r="162" spans="5:12" ht="18">
       <c r="E162"/>
       <c r="F162"/>
       <c r="G162"/>
@@ -10312,7 +10341,7 @@
       <c r="K162"/>
       <c r="L162"/>
     </row>
-    <row r="163" spans="5:12" ht="18.75">
+    <row r="163" spans="5:12" ht="18">
       <c r="E163"/>
       <c r="F163"/>
       <c r="G163"/>
@@ -10322,7 +10351,7 @@
       <c r="K163"/>
       <c r="L163"/>
     </row>
-    <row r="164" spans="5:12" ht="18.75">
+    <row r="164" spans="5:12" ht="18">
       <c r="E164"/>
       <c r="F164"/>
       <c r="G164"/>
@@ -10332,7 +10361,7 @@
       <c r="K164"/>
       <c r="L164"/>
     </row>
-    <row r="165" spans="5:12" ht="18.75">
+    <row r="165" spans="5:12" ht="18">
       <c r="E165"/>
       <c r="F165"/>
       <c r="G165"/>
@@ -10342,7 +10371,7 @@
       <c r="K165"/>
       <c r="L165"/>
     </row>
-    <row r="166" spans="5:12" ht="18.75">
+    <row r="166" spans="5:12" ht="18">
       <c r="E166"/>
       <c r="F166"/>
       <c r="G166"/>
@@ -10352,7 +10381,7 @@
       <c r="K166"/>
       <c r="L166"/>
     </row>
-    <row r="167" spans="5:12" ht="18.75">
+    <row r="167" spans="5:12" ht="18">
       <c r="E167"/>
       <c r="F167"/>
       <c r="G167"/>
@@ -10362,7 +10391,7 @@
       <c r="K167"/>
       <c r="L167"/>
     </row>
-    <row r="168" spans="5:12" ht="18.75">
+    <row r="168" spans="5:12" ht="18">
       <c r="E168"/>
       <c r="F168"/>
       <c r="G168"/>
@@ -10372,7 +10401,7 @@
       <c r="K168"/>
       <c r="L168"/>
     </row>
-    <row r="169" spans="5:12" ht="18.75">
+    <row r="169" spans="5:12" ht="18">
       <c r="E169"/>
       <c r="F169"/>
       <c r="G169"/>
@@ -10382,7 +10411,7 @@
       <c r="K169"/>
       <c r="L169"/>
     </row>
-    <row r="170" spans="5:12" ht="18.75">
+    <row r="170" spans="5:12" ht="18">
       <c r="E170"/>
       <c r="F170"/>
       <c r="G170"/>
@@ -10392,7 +10421,7 @@
       <c r="K170"/>
       <c r="L170"/>
     </row>
-    <row r="171" spans="5:12" ht="18.75">
+    <row r="171" spans="5:12" ht="18">
       <c r="E171"/>
       <c r="F171"/>
       <c r="G171"/>
@@ -10402,7 +10431,7 @@
       <c r="K171"/>
       <c r="L171"/>
     </row>
-    <row r="172" spans="5:12" ht="18.75">
+    <row r="172" spans="5:12" ht="18">
       <c r="E172"/>
       <c r="F172"/>
       <c r="G172"/>
@@ -10412,7 +10441,7 @@
       <c r="K172"/>
       <c r="L172"/>
     </row>
-    <row r="173" spans="5:12" ht="18.75">
+    <row r="173" spans="5:12" ht="18">
       <c r="E173"/>
       <c r="F173"/>
       <c r="G173"/>
@@ -10422,7 +10451,7 @@
       <c r="K173"/>
       <c r="L173"/>
     </row>
-    <row r="174" spans="5:12" ht="18.75">
+    <row r="174" spans="5:12" ht="18">
       <c r="E174"/>
       <c r="F174"/>
       <c r="G174"/>
@@ -10432,7 +10461,7 @@
       <c r="K174"/>
       <c r="L174"/>
     </row>
-    <row r="175" spans="5:12" ht="18.75">
+    <row r="175" spans="5:12" ht="18">
       <c r="E175"/>
       <c r="F175"/>
       <c r="G175"/>
@@ -10442,7 +10471,7 @@
       <c r="K175"/>
       <c r="L175"/>
     </row>
-    <row r="176" spans="5:12" ht="18.75">
+    <row r="176" spans="5:12" ht="18">
       <c r="E176"/>
       <c r="F176"/>
       <c r="G176"/>
@@ -10452,7 +10481,7 @@
       <c r="K176"/>
       <c r="L176"/>
     </row>
-    <row r="177" spans="5:12" ht="18.75">
+    <row r="177" spans="5:12" ht="18">
       <c r="E177"/>
       <c r="F177"/>
       <c r="G177"/>
@@ -10462,7 +10491,7 @@
       <c r="K177"/>
       <c r="L177"/>
     </row>
-    <row r="178" spans="5:12" ht="18.75">
+    <row r="178" spans="5:12" ht="18">
       <c r="E178"/>
       <c r="F178"/>
       <c r="G178"/>
@@ -10472,7 +10501,7 @@
       <c r="K178"/>
       <c r="L178"/>
     </row>
-    <row r="179" spans="5:12" ht="18.75">
+    <row r="179" spans="5:12" ht="18">
       <c r="E179"/>
       <c r="F179"/>
       <c r="G179"/>
@@ -10482,7 +10511,7 @@
       <c r="K179"/>
       <c r="L179"/>
     </row>
-    <row r="180" spans="5:12" ht="18.75">
+    <row r="180" spans="5:12" ht="18">
       <c r="E180"/>
       <c r="F180"/>
       <c r="G180"/>
@@ -10492,7 +10521,7 @@
       <c r="K180"/>
       <c r="L180"/>
     </row>
-    <row r="181" spans="5:12" ht="18.75">
+    <row r="181" spans="5:12" ht="18">
       <c r="E181"/>
       <c r="F181"/>
       <c r="G181"/>
@@ -10502,7 +10531,7 @@
       <c r="K181"/>
       <c r="L181"/>
     </row>
-    <row r="182" spans="5:12" ht="18.75">
+    <row r="182" spans="5:12" ht="18">
       <c r="E182"/>
       <c r="F182"/>
       <c r="G182"/>
@@ -10512,7 +10541,7 @@
       <c r="K182"/>
       <c r="L182"/>
     </row>
-    <row r="183" spans="5:12" ht="18.75">
+    <row r="183" spans="5:12" ht="18">
       <c r="E183"/>
       <c r="F183"/>
       <c r="G183"/>
@@ -10522,7 +10551,7 @@
       <c r="K183"/>
       <c r="L183"/>
     </row>
-    <row r="184" spans="5:12" ht="18.75">
+    <row r="184" spans="5:12" ht="18">
       <c r="E184"/>
       <c r="F184"/>
       <c r="G184"/>
@@ -10532,7 +10561,7 @@
       <c r="K184"/>
       <c r="L184"/>
     </row>
-    <row r="185" spans="5:12" ht="18.75">
+    <row r="185" spans="5:12" ht="18">
       <c r="E185"/>
       <c r="F185"/>
       <c r="G185"/>
@@ -10542,7 +10571,7 @@
       <c r="K185"/>
       <c r="L185"/>
     </row>
-    <row r="186" spans="5:12" ht="18.75">
+    <row r="186" spans="5:12" ht="18">
       <c r="E186"/>
       <c r="F186"/>
       <c r="G186"/>
@@ -10552,7 +10581,7 @@
       <c r="K186"/>
       <c r="L186"/>
     </row>
-    <row r="187" spans="5:12" ht="18.75">
+    <row r="187" spans="5:12" ht="18">
       <c r="E187"/>
       <c r="F187"/>
       <c r="G187"/>
@@ -10562,7 +10591,7 @@
       <c r="K187"/>
       <c r="L187"/>
     </row>
-    <row r="188" spans="5:12" ht="18.75">
+    <row r="188" spans="5:12" ht="18">
       <c r="E188"/>
       <c r="F188"/>
       <c r="G188"/>
@@ -10572,7 +10601,7 @@
       <c r="K188"/>
       <c r="L188"/>
     </row>
-    <row r="189" spans="5:12" ht="18.75">
+    <row r="189" spans="5:12" ht="18">
       <c r="E189"/>
       <c r="F189"/>
       <c r="G189"/>
@@ -10582,7 +10611,7 @@
       <c r="K189"/>
       <c r="L189"/>
     </row>
-    <row r="190" spans="5:12" ht="18.75">
+    <row r="190" spans="5:12" ht="18">
       <c r="E190"/>
       <c r="F190"/>
       <c r="G190"/>
@@ -10592,7 +10621,7 @@
       <c r="K190"/>
       <c r="L190"/>
     </row>
-    <row r="191" spans="5:12" ht="18.75">
+    <row r="191" spans="5:12" ht="18">
       <c r="E191"/>
       <c r="F191"/>
       <c r="G191"/>
@@ -10602,7 +10631,7 @@
       <c r="K191"/>
       <c r="L191"/>
     </row>
-    <row r="192" spans="5:12" ht="18.75">
+    <row r="192" spans="5:12" ht="18">
       <c r="E192"/>
       <c r="F192"/>
       <c r="G192"/>
@@ -10612,7 +10641,7 @@
       <c r="K192"/>
       <c r="L192"/>
     </row>
-    <row r="193" spans="5:12" ht="18.75">
+    <row r="193" spans="5:12" ht="18">
       <c r="E193"/>
       <c r="F193"/>
       <c r="G193"/>
@@ -10622,7 +10651,7 @@
       <c r="K193"/>
       <c r="L193"/>
     </row>
-    <row r="194" spans="5:12" ht="18.75">
+    <row r="194" spans="5:12" ht="18">
       <c r="E194"/>
       <c r="F194"/>
       <c r="G194"/>
@@ -10632,7 +10661,7 @@
       <c r="K194"/>
       <c r="L194"/>
     </row>
-    <row r="195" spans="5:12" ht="18.75">
+    <row r="195" spans="5:12" ht="18">
       <c r="E195"/>
       <c r="F195"/>
       <c r="G195"/>
@@ -10642,7 +10671,7 @@
       <c r="K195"/>
       <c r="L195"/>
     </row>
-    <row r="196" spans="5:12" ht="18.75">
+    <row r="196" spans="5:12" ht="18">
       <c r="E196"/>
       <c r="F196"/>
       <c r="G196"/>
@@ -10652,7 +10681,7 @@
       <c r="K196"/>
       <c r="L196"/>
     </row>
-    <row r="197" spans="5:12" ht="18.75">
+    <row r="197" spans="5:12" ht="18">
       <c r="E197"/>
       <c r="F197"/>
       <c r="G197"/>
@@ -10662,7 +10691,7 @@
       <c r="K197"/>
       <c r="L197"/>
     </row>
-    <row r="198" spans="5:12" ht="18.75">
+    <row r="198" spans="5:12" ht="18">
       <c r="E198"/>
       <c r="F198"/>
       <c r="G198"/>
@@ -10672,7 +10701,7 @@
       <c r="K198"/>
       <c r="L198"/>
     </row>
-    <row r="199" spans="5:12" ht="18.75">
+    <row r="199" spans="5:12" ht="18">
       <c r="E199"/>
       <c r="F199"/>
       <c r="G199"/>
@@ -10682,7 +10711,7 @@
       <c r="K199"/>
       <c r="L199"/>
     </row>
-    <row r="200" spans="5:12" ht="18.75">
+    <row r="200" spans="5:12" ht="18">
       <c r="E200"/>
       <c r="F200"/>
       <c r="G200"/>
@@ -10692,7 +10721,7 @@
       <c r="K200"/>
       <c r="L200"/>
     </row>
-    <row r="201" spans="5:12" ht="18.75">
+    <row r="201" spans="5:12" ht="18">
       <c r="E201"/>
       <c r="F201"/>
       <c r="G201"/>
@@ -10702,7 +10731,7 @@
       <c r="K201"/>
       <c r="L201"/>
     </row>
-    <row r="202" spans="5:12" ht="18.75">
+    <row r="202" spans="5:12" ht="18">
       <c r="E202"/>
       <c r="F202"/>
       <c r="G202"/>
@@ -10712,7 +10741,7 @@
       <c r="K202"/>
       <c r="L202"/>
     </row>
-    <row r="203" spans="5:12" ht="18.75">
+    <row r="203" spans="5:12" ht="18">
       <c r="E203"/>
       <c r="F203"/>
       <c r="G203"/>
@@ -10722,7 +10751,7 @@
       <c r="K203"/>
       <c r="L203"/>
     </row>
-    <row r="204" spans="5:12" ht="18.75">
+    <row r="204" spans="5:12" ht="18">
       <c r="E204"/>
       <c r="F204"/>
       <c r="G204"/>
@@ -10732,7 +10761,7 @@
       <c r="K204"/>
       <c r="L204"/>
     </row>
-    <row r="205" spans="5:12" ht="18.75">
+    <row r="205" spans="5:12" ht="18">
       <c r="E205"/>
       <c r="F205"/>
       <c r="G205"/>
@@ -10742,7 +10771,7 @@
       <c r="K205"/>
       <c r="L205"/>
     </row>
-    <row r="206" spans="5:12" ht="18.75">
+    <row r="206" spans="5:12" ht="18">
       <c r="E206"/>
       <c r="F206"/>
       <c r="G206"/>
@@ -10752,7 +10781,7 @@
       <c r="K206"/>
       <c r="L206"/>
     </row>
-    <row r="207" spans="5:12" ht="18.75">
+    <row r="207" spans="5:12" ht="18">
       <c r="E207"/>
       <c r="F207"/>
       <c r="G207"/>
@@ -10762,7 +10791,7 @@
       <c r="K207"/>
       <c r="L207"/>
     </row>
-    <row r="208" spans="5:12" ht="18.75">
+    <row r="208" spans="5:12" ht="18">
       <c r="E208"/>
       <c r="F208"/>
       <c r="G208"/>
@@ -10772,7 +10801,7 @@
       <c r="K208"/>
       <c r="L208"/>
     </row>
-    <row r="209" spans="5:12" ht="18.75">
+    <row r="209" spans="5:12" ht="18">
       <c r="E209"/>
       <c r="F209"/>
       <c r="G209"/>
@@ -10782,7 +10811,7 @@
       <c r="K209"/>
       <c r="L209"/>
     </row>
-    <row r="210" spans="5:12" ht="18.75">
+    <row r="210" spans="5:12" ht="18">
       <c r="E210"/>
       <c r="F210"/>
       <c r="G210"/>
@@ -10792,7 +10821,7 @@
       <c r="K210"/>
       <c r="L210"/>
     </row>
-    <row r="211" spans="5:12" ht="18.75">
+    <row r="211" spans="5:12" ht="18">
       <c r="E211"/>
       <c r="F211"/>
       <c r="G211"/>
@@ -10802,7 +10831,7 @@
       <c r="K211"/>
       <c r="L211"/>
     </row>
-    <row r="212" spans="5:12" ht="18.75">
+    <row r="212" spans="5:12" ht="18">
       <c r="E212"/>
       <c r="F212"/>
       <c r="G212"/>
@@ -10812,7 +10841,7 @@
       <c r="K212"/>
       <c r="L212"/>
     </row>
-    <row r="213" spans="5:12" ht="18.75">
+    <row r="213" spans="5:12" ht="18">
       <c r="E213"/>
       <c r="F213"/>
       <c r="G213"/>
@@ -10822,7 +10851,7 @@
       <c r="K213"/>
       <c r="L213"/>
     </row>
-    <row r="214" spans="5:12" ht="18.75">
+    <row r="214" spans="5:12" ht="18">
       <c r="E214"/>
       <c r="F214"/>
       <c r="G214"/>
@@ -10832,7 +10861,7 @@
       <c r="K214"/>
       <c r="L214"/>
     </row>
-    <row r="215" spans="5:12" ht="18.75">
+    <row r="215" spans="5:12" ht="18">
       <c r="E215"/>
       <c r="F215"/>
       <c r="G215"/>
@@ -10842,7 +10871,7 @@
       <c r="K215"/>
       <c r="L215"/>
     </row>
-    <row r="216" spans="5:12" ht="18.75">
+    <row r="216" spans="5:12" ht="18">
       <c r="E216"/>
       <c r="F216"/>
       <c r="G216"/>
@@ -10852,7 +10881,7 @@
       <c r="K216"/>
       <c r="L216"/>
     </row>
-    <row r="217" spans="5:12" ht="18.75">
+    <row r="217" spans="5:12" ht="18">
       <c r="E217"/>
       <c r="F217"/>
       <c r="G217"/>
@@ -10862,7 +10891,7 @@
       <c r="K217"/>
       <c r="L217"/>
     </row>
-    <row r="218" spans="5:12" ht="18.75">
+    <row r="218" spans="5:12" ht="18">
       <c r="E218"/>
       <c r="F218"/>
       <c r="G218"/>
@@ -10872,7 +10901,7 @@
       <c r="K218"/>
       <c r="L218"/>
     </row>
-    <row r="219" spans="5:12" ht="18.75">
+    <row r="219" spans="5:12" ht="18">
       <c r="E219"/>
       <c r="F219"/>
       <c r="G219"/>
@@ -10882,7 +10911,7 @@
       <c r="K219"/>
       <c r="L219"/>
     </row>
-    <row r="220" spans="5:12" ht="18.75">
+    <row r="220" spans="5:12" ht="18">
       <c r="E220"/>
       <c r="F220"/>
       <c r="G220"/>
@@ -10892,7 +10921,7 @@
       <c r="K220"/>
       <c r="L220"/>
     </row>
-    <row r="221" spans="5:12" ht="18.75">
+    <row r="221" spans="5:12" ht="18">
       <c r="E221"/>
       <c r="F221"/>
       <c r="G221"/>
@@ -10902,7 +10931,7 @@
       <c r="K221"/>
       <c r="L221"/>
     </row>
-    <row r="222" spans="5:12" ht="18.75">
+    <row r="222" spans="5:12" ht="18">
       <c r="E222"/>
       <c r="F222"/>
       <c r="G222"/>
@@ -10912,7 +10941,7 @@
       <c r="K222"/>
       <c r="L222"/>
     </row>
-    <row r="223" spans="5:12" ht="18.75">
+    <row r="223" spans="5:12" ht="18">
       <c r="E223"/>
       <c r="F223"/>
       <c r="G223"/>
@@ -10922,7 +10951,7 @@
       <c r="K223"/>
       <c r="L223"/>
     </row>
-    <row r="224" spans="5:12" ht="18.75">
+    <row r="224" spans="5:12" ht="18">
       <c r="E224"/>
       <c r="F224"/>
       <c r="G224"/>
@@ -10932,7 +10961,7 @@
       <c r="K224"/>
       <c r="L224"/>
     </row>
-    <row r="225" spans="5:12" ht="18.75">
+    <row r="225" spans="5:12" ht="18">
       <c r="E225"/>
       <c r="F225"/>
       <c r="G225"/>
@@ -10942,7 +10971,7 @@
       <c r="K225"/>
       <c r="L225"/>
     </row>
-    <row r="226" spans="5:12" ht="18.75">
+    <row r="226" spans="5:12" ht="18">
       <c r="E226"/>
       <c r="F226"/>
       <c r="G226"/>
@@ -10952,7 +10981,7 @@
       <c r="K226"/>
       <c r="L226"/>
     </row>
-    <row r="227" spans="5:12" ht="18.75">
+    <row r="227" spans="5:12" ht="18">
       <c r="E227"/>
       <c r="F227"/>
       <c r="G227"/>
@@ -10962,7 +10991,7 @@
       <c r="K227"/>
       <c r="L227"/>
     </row>
-    <row r="228" spans="5:12" ht="18.75">
+    <row r="228" spans="5:12" ht="18">
       <c r="E228"/>
       <c r="F228"/>
       <c r="G228"/>
@@ -10972,7 +11001,7 @@
       <c r="K228"/>
       <c r="L228"/>
     </row>
-    <row r="229" spans="5:12" ht="18.75">
+    <row r="229" spans="5:12" ht="18">
       <c r="E229"/>
       <c r="F229"/>
       <c r="G229"/>
@@ -10982,7 +11011,7 @@
       <c r="K229"/>
       <c r="L229"/>
     </row>
-    <row r="230" spans="5:12" ht="18.75">
+    <row r="230" spans="5:12" ht="18">
       <c r="E230"/>
       <c r="F230"/>
       <c r="G230"/>
@@ -10992,7 +11021,7 @@
       <c r="K230"/>
       <c r="L230"/>
     </row>
-    <row r="231" spans="5:12" ht="18.75">
+    <row r="231" spans="5:12" ht="18">
       <c r="E231"/>
       <c r="F231"/>
       <c r="G231"/>
@@ -11002,7 +11031,7 @@
       <c r="K231"/>
       <c r="L231"/>
     </row>
-    <row r="232" spans="5:12" ht="18.75">
+    <row r="232" spans="5:12" ht="18">
       <c r="E232"/>
       <c r="F232"/>
       <c r="G232"/>
@@ -11012,7 +11041,7 @@
       <c r="K232"/>
       <c r="L232"/>
     </row>
-    <row r="233" spans="5:12" ht="18.75">
+    <row r="233" spans="5:12" ht="18">
       <c r="E233"/>
       <c r="F233"/>
       <c r="G233"/>
@@ -11022,7 +11051,7 @@
       <c r="K233"/>
       <c r="L233"/>
     </row>
-    <row r="234" spans="5:12" ht="18.75">
+    <row r="234" spans="5:12" ht="18">
       <c r="E234"/>
       <c r="F234"/>
       <c r="G234"/>
@@ -11032,7 +11061,7 @@
       <c r="K234"/>
       <c r="L234"/>
     </row>
-    <row r="235" spans="5:12" ht="18.75">
+    <row r="235" spans="5:12" ht="18">
       <c r="E235"/>
       <c r="F235"/>
       <c r="G235"/>
@@ -11042,7 +11071,7 @@
       <c r="K235"/>
       <c r="L235"/>
     </row>
-    <row r="236" spans="5:12" ht="18.75">
+    <row r="236" spans="5:12" ht="18">
       <c r="E236"/>
       <c r="F236"/>
       <c r="G236"/>
@@ -11052,7 +11081,7 @@
       <c r="K236"/>
       <c r="L236"/>
     </row>
-    <row r="237" spans="5:12" ht="18.75">
+    <row r="237" spans="5:12" ht="18">
       <c r="E237"/>
       <c r="F237"/>
       <c r="G237"/>
@@ -11062,7 +11091,7 @@
       <c r="K237"/>
       <c r="L237"/>
     </row>
-    <row r="238" spans="5:12" ht="18.75">
+    <row r="238" spans="5:12" ht="18">
       <c r="E238"/>
       <c r="F238"/>
       <c r="G238"/>
@@ -11072,7 +11101,7 @@
       <c r="K238"/>
       <c r="L238"/>
     </row>
-    <row r="239" spans="5:12" ht="18.75">
+    <row r="239" spans="5:12" ht="18">
       <c r="E239"/>
       <c r="F239"/>
       <c r="G239"/>
@@ -11082,7 +11111,7 @@
       <c r="K239"/>
       <c r="L239"/>
     </row>
-    <row r="240" spans="5:12" ht="18.75">
+    <row r="240" spans="5:12" ht="18">
       <c r="E240"/>
       <c r="F240"/>
       <c r="G240"/>
@@ -11092,7 +11121,7 @@
       <c r="K240"/>
       <c r="L240"/>
     </row>
-    <row r="241" spans="5:12" ht="18.75">
+    <row r="241" spans="5:12" ht="18">
       <c r="E241"/>
       <c r="F241"/>
       <c r="G241"/>
@@ -11102,7 +11131,7 @@
       <c r="K241"/>
       <c r="L241"/>
     </row>
-    <row r="242" spans="5:12" ht="18.75">
+    <row r="242" spans="5:12" ht="18">
       <c r="E242"/>
       <c r="F242"/>
       <c r="G242"/>
@@ -11112,7 +11141,7 @@
       <c r="K242"/>
       <c r="L242"/>
     </row>
-    <row r="243" spans="5:12" ht="18.75">
+    <row r="243" spans="5:12" ht="18">
       <c r="E243"/>
       <c r="F243"/>
       <c r="G243"/>
@@ -11122,7 +11151,7 @@
       <c r="K243"/>
       <c r="L243"/>
     </row>
-    <row r="244" spans="5:12" ht="18.75">
+    <row r="244" spans="5:12" ht="18">
       <c r="E244"/>
       <c r="F244"/>
       <c r="G244"/>
@@ -11132,7 +11161,7 @@
       <c r="K244"/>
       <c r="L244"/>
     </row>
-    <row r="245" spans="5:12" ht="18.75">
+    <row r="245" spans="5:12" ht="18">
       <c r="E245"/>
       <c r="F245"/>
       <c r="G245"/>
@@ -11142,7 +11171,7 @@
       <c r="K245"/>
       <c r="L245"/>
     </row>
-    <row r="246" spans="5:12" ht="18.75">
+    <row r="246" spans="5:12" ht="18">
       <c r="E246"/>
       <c r="F246"/>
       <c r="G246"/>
@@ -11152,7 +11181,7 @@
       <c r="K246"/>
       <c r="L246"/>
     </row>
-    <row r="247" spans="5:12" ht="18.75">
+    <row r="247" spans="5:12" ht="18">
       <c r="E247"/>
       <c r="F247"/>
       <c r="G247"/>
@@ -11162,7 +11191,7 @@
       <c r="K247"/>
       <c r="L247"/>
     </row>
-    <row r="248" spans="5:12" ht="18.75">
+    <row r="248" spans="5:12" ht="18">
       <c r="E248"/>
       <c r="F248"/>
       <c r="G248"/>
@@ -11172,7 +11201,7 @@
       <c r="K248"/>
       <c r="L248"/>
     </row>
-    <row r="249" spans="5:12" ht="18.75">
+    <row r="249" spans="5:12" ht="18">
       <c r="E249"/>
       <c r="F249"/>
       <c r="G249"/>
@@ -11182,7 +11211,7 @@
       <c r="K249"/>
       <c r="L249"/>
     </row>
-    <row r="250" spans="5:12" ht="18.75">
+    <row r="250" spans="5:12" ht="18">
       <c r="E250"/>
       <c r="F250"/>
       <c r="G250"/>
@@ -11192,7 +11221,7 @@
       <c r="K250"/>
       <c r="L250"/>
     </row>
-    <row r="251" spans="5:12" ht="18.75">
+    <row r="251" spans="5:12" ht="18">
       <c r="E251"/>
       <c r="F251"/>
       <c r="G251"/>
@@ -11202,7 +11231,7 @@
       <c r="K251"/>
       <c r="L251"/>
     </row>
-    <row r="252" spans="5:12" ht="18.75">
+    <row r="252" spans="5:12" ht="18">
       <c r="E252"/>
       <c r="F252"/>
       <c r="G252"/>
@@ -11212,7 +11241,7 @@
       <c r="K252"/>
       <c r="L252"/>
     </row>
-    <row r="253" spans="5:12" ht="18.75">
+    <row r="253" spans="5:12" ht="18">
       <c r="E253"/>
       <c r="F253"/>
       <c r="G253"/>
@@ -11222,7 +11251,7 @@
       <c r="K253"/>
       <c r="L253"/>
     </row>
-    <row r="254" spans="5:12" ht="18.75">
+    <row r="254" spans="5:12" ht="18">
       <c r="E254"/>
       <c r="F254"/>
       <c r="G254"/>
@@ -11232,7 +11261,7 @@
       <c r="K254"/>
       <c r="L254"/>
     </row>
-    <row r="255" spans="5:12" ht="18.75">
+    <row r="255" spans="5:12" ht="18">
       <c r="E255"/>
       <c r="F255"/>
       <c r="G255"/>
@@ -11242,7 +11271,7 @@
       <c r="K255"/>
       <c r="L255"/>
     </row>
-    <row r="256" spans="5:12" ht="18.75">
+    <row r="256" spans="5:12" ht="18">
       <c r="E256"/>
       <c r="F256"/>
       <c r="G256"/>
@@ -11252,7 +11281,7 @@
       <c r="K256"/>
       <c r="L256"/>
     </row>
-    <row r="257" spans="5:12" ht="18.75">
+    <row r="257" spans="5:12" ht="18">
       <c r="E257"/>
       <c r="F257"/>
       <c r="G257"/>
@@ -11262,7 +11291,7 @@
       <c r="K257"/>
       <c r="L257"/>
     </row>
-    <row r="258" spans="5:12" ht="18.75">
+    <row r="258" spans="5:12" ht="18">
       <c r="E258"/>
       <c r="F258"/>
       <c r="G258"/>
@@ -11272,7 +11301,7 @@
       <c r="K258"/>
       <c r="L258"/>
     </row>
-    <row r="259" spans="5:12" ht="18.75">
+    <row r="259" spans="5:12" ht="18">
       <c r="E259"/>
       <c r="F259"/>
       <c r="G259"/>
@@ -11282,7 +11311,7 @@
       <c r="K259"/>
       <c r="L259"/>
     </row>
-    <row r="260" spans="5:12" ht="18.75">
+    <row r="260" spans="5:12" ht="18">
       <c r="E260"/>
       <c r="F260"/>
       <c r="G260"/>
@@ -11292,7 +11321,7 @@
       <c r="K260"/>
       <c r="L260"/>
     </row>
-    <row r="261" spans="5:12" ht="18.75">
+    <row r="261" spans="5:12" ht="18">
       <c r="E261"/>
       <c r="F261"/>
       <c r="G261"/>
@@ -11302,7 +11331,7 @@
       <c r="K261"/>
       <c r="L261"/>
     </row>
-    <row r="262" spans="5:12" ht="18.75">
+    <row r="262" spans="5:12" ht="18">
       <c r="E262"/>
       <c r="F262"/>
       <c r="G262"/>
@@ -11312,7 +11341,7 @@
       <c r="K262"/>
       <c r="L262"/>
     </row>
-    <row r="263" spans="5:12" ht="18.75">
+    <row r="263" spans="5:12" ht="18">
       <c r="E263"/>
       <c r="F263"/>
       <c r="G263"/>
@@ -11322,7 +11351,7 @@
       <c r="K263"/>
       <c r="L263"/>
     </row>
-    <row r="264" spans="5:12" ht="18.75">
+    <row r="264" spans="5:12" ht="18">
       <c r="E264"/>
       <c r="F264"/>
       <c r="G264"/>
@@ -11332,7 +11361,7 @@
       <c r="K264"/>
       <c r="L264"/>
     </row>
-    <row r="265" spans="5:12" ht="18.75">
+    <row r="265" spans="5:12" ht="18">
       <c r="E265"/>
       <c r="F265"/>
       <c r="G265"/>
@@ -11342,7 +11371,7 @@
       <c r="K265"/>
       <c r="L265"/>
     </row>
-    <row r="266" spans="5:12" ht="18.75">
+    <row r="266" spans="5:12" ht="18">
       <c r="E266"/>
       <c r="F266"/>
       <c r="G266"/>
@@ -11352,7 +11381,7 @@
       <c r="K266"/>
       <c r="L266"/>
     </row>
-    <row r="267" spans="5:12" ht="18.75">
+    <row r="267" spans="5:12" ht="18">
       <c r="E267"/>
       <c r="F267"/>
       <c r="G267"/>
@@ -11362,7 +11391,7 @@
       <c r="K267"/>
       <c r="L267"/>
     </row>
-    <row r="268" spans="5:12" ht="18.75">
+    <row r="268" spans="5:12" ht="18">
       <c r="E268"/>
       <c r="F268"/>
       <c r="G268"/>
@@ -11372,7 +11401,7 @@
       <c r="K268"/>
       <c r="L268"/>
     </row>
-    <row r="269" spans="5:12" ht="18.75">
+    <row r="269" spans="5:12" ht="18">
       <c r="E269"/>
       <c r="F269"/>
       <c r="G269"/>
@@ -11382,7 +11411,7 @@
       <c r="K269"/>
       <c r="L269"/>
     </row>
-    <row r="270" spans="5:12" ht="18.75">
+    <row r="270" spans="5:12" ht="18">
       <c r="E270"/>
       <c r="F270"/>
       <c r="G270"/>
@@ -11392,7 +11421,7 @@
       <c r="K270"/>
       <c r="L270"/>
     </row>
-    <row r="271" spans="5:12" ht="18.75">
+    <row r="271" spans="5:12" ht="18">
       <c r="E271"/>
       <c r="F271"/>
       <c r="G271"/>
@@ -11402,7 +11431,7 @@
       <c r="K271"/>
       <c r="L271"/>
     </row>
-    <row r="272" spans="5:12" ht="18.75">
+    <row r="272" spans="5:12" ht="18">
       <c r="E272"/>
       <c r="F272"/>
       <c r="G272"/>
@@ -11412,7 +11441,7 @@
       <c r="K272"/>
       <c r="L272"/>
     </row>
-    <row r="273" spans="5:12" ht="18.75">
+    <row r="273" spans="5:12" ht="18">
       <c r="E273"/>
       <c r="F273"/>
       <c r="G273"/>
@@ -11422,7 +11451,7 @@
       <c r="K273"/>
       <c r="L273"/>
     </row>
-    <row r="274" spans="5:12" ht="18.75">
+    <row r="274" spans="5:12" ht="18">
       <c r="E274"/>
       <c r="F274"/>
       <c r="G274"/>
@@ -11432,7 +11461,7 @@
       <c r="K274"/>
       <c r="L274"/>
     </row>
-    <row r="275" spans="5:12" ht="18.75">
+    <row r="275" spans="5:12" ht="18">
       <c r="E275"/>
       <c r="F275"/>
       <c r="G275"/>
@@ -11442,7 +11471,7 @@
       <c r="K275"/>
       <c r="L275"/>
     </row>
-    <row r="276" spans="5:12" ht="18.75">
+    <row r="276" spans="5:12" ht="18">
       <c r="E276"/>
       <c r="F276"/>
       <c r="G276"/>
@@ -11452,7 +11481,7 @@
       <c r="K276"/>
       <c r="L276"/>
     </row>
-    <row r="277" spans="5:12" ht="18.75">
+    <row r="277" spans="5:12" ht="18">
       <c r="E277"/>
       <c r="F277"/>
       <c r="G277"/>
@@ -11462,7 +11491,7 @@
       <c r="K277"/>
       <c r="L277"/>
     </row>
-    <row r="278" spans="5:12" ht="18.75">
+    <row r="278" spans="5:12" ht="18">
       <c r="E278"/>
       <c r="F278"/>
       <c r="G278"/>
@@ -11472,7 +11501,7 @@
       <c r="K278"/>
       <c r="L278"/>
     </row>
-    <row r="279" spans="5:12" ht="18.75">
+    <row r="279" spans="5:12" ht="18">
       <c r="E279"/>
       <c r="F279"/>
       <c r="G279"/>
@@ -11482,7 +11511,7 @@
       <c r="K279"/>
       <c r="L279"/>
     </row>
-    <row r="280" spans="5:12" ht="18.75">
+    <row r="280" spans="5:12" ht="18">
       <c r="E280"/>
       <c r="F280"/>
       <c r="G280"/>
@@ -11492,7 +11521,7 @@
       <c r="K280"/>
       <c r="L280"/>
     </row>
-    <row r="281" spans="5:12" ht="18.75">
+    <row r="281" spans="5:12" ht="18">
       <c r="E281"/>
       <c r="F281"/>
       <c r="G281"/>
@@ -11502,7 +11531,7 @@
       <c r="K281"/>
       <c r="L281"/>
     </row>
-    <row r="282" spans="5:12" ht="18.75">
+    <row r="282" spans="5:12" ht="18">
       <c r="E282"/>
       <c r="F282"/>
       <c r="G282"/>
@@ -11512,7 +11541,7 @@
       <c r="K282"/>
       <c r="L282"/>
     </row>
-    <row r="283" spans="5:12" ht="18.75">
+    <row r="283" spans="5:12" ht="18">
       <c r="E283"/>
       <c r="F283"/>
       <c r="G283"/>
@@ -11522,7 +11551,7 @@
       <c r="K283"/>
       <c r="L283"/>
     </row>
-    <row r="284" spans="5:12" ht="18.75">
+    <row r="284" spans="5:12" ht="18">
       <c r="E284"/>
       <c r="F284"/>
       <c r="G284"/>
@@ -11532,7 +11561,7 @@
       <c r="K284"/>
       <c r="L284"/>
     </row>
-    <row r="285" spans="5:12" ht="18.75">
+    <row r="285" spans="5:12" ht="18">
       <c r="E285"/>
       <c r="F285"/>
       <c r="G285"/>
@@ -11542,7 +11571,7 @@
       <c r="K285"/>
       <c r="L285"/>
     </row>
-    <row r="286" spans="5:12" ht="18.75">
+    <row r="286" spans="5:12" ht="18">
       <c r="E286"/>
       <c r="F286"/>
       <c r="G286"/>
@@ -11552,7 +11581,7 @@
       <c r="K286"/>
       <c r="L286"/>
     </row>
-    <row r="287" spans="5:12" ht="18.75">
+    <row r="287" spans="5:12" ht="18">
       <c r="E287"/>
       <c r="F287"/>
       <c r="G287"/>
@@ -11562,7 +11591,7 @@
       <c r="K287"/>
       <c r="L287"/>
     </row>
-    <row r="288" spans="5:12" ht="18.75">
+    <row r="288" spans="5:12" ht="18">
       <c r="E288"/>
       <c r="F288"/>
       <c r="G288"/>
@@ -11572,7 +11601,7 @@
       <c r="K288"/>
       <c r="L288"/>
     </row>
-    <row r="289" spans="5:12" ht="18.75">
+    <row r="289" spans="5:12" ht="18">
       <c r="E289"/>
       <c r="F289"/>
       <c r="G289"/>
@@ -11582,7 +11611,7 @@
       <c r="K289"/>
       <c r="L289"/>
     </row>
-    <row r="290" spans="5:12" ht="18.75">
+    <row r="290" spans="5:12" ht="18">
       <c r="E290"/>
       <c r="F290"/>
       <c r="G290"/>
@@ -11592,7 +11621,7 @@
       <c r="K290"/>
       <c r="L290"/>
     </row>
-    <row r="291" spans="5:12" ht="18.75">
+    <row r="291" spans="5:12" ht="18">
       <c r="E291"/>
       <c r="F291"/>
       <c r="G291"/>
@@ -11602,7 +11631,7 @@
       <c r="K291"/>
       <c r="L291"/>
     </row>
-    <row r="292" spans="5:12" ht="18.75">
+    <row r="292" spans="5:12" ht="18">
       <c r="E292"/>
       <c r="F292"/>
       <c r="G292"/>
@@ -11612,7 +11641,7 @@
       <c r="K292"/>
       <c r="L292"/>
     </row>
-    <row r="293" spans="5:12" ht="18.75">
+    <row r="293" spans="5:12" ht="18">
       <c r="E293"/>
       <c r="F293"/>
       <c r="G293"/>
@@ -11622,7 +11651,7 @@
       <c r="K293"/>
       <c r="L293"/>
     </row>
-    <row r="294" spans="5:12" ht="18.75">
+    <row r="294" spans="5:12" ht="18">
       <c r="E294"/>
       <c r="F294"/>
       <c r="G294"/>
@@ -11632,7 +11661,7 @@
       <c r="K294"/>
       <c r="L294"/>
     </row>
-    <row r="295" spans="5:12" ht="18.75">
+    <row r="295" spans="5:12" ht="18">
       <c r="E295"/>
       <c r="F295"/>
       <c r="G295"/>
@@ -11642,7 +11671,7 @@
       <c r="K295"/>
       <c r="L295"/>
     </row>
-    <row r="296" spans="5:12" ht="18.75">
+    <row r="296" spans="5:12" ht="18">
       <c r="E296"/>
       <c r="F296"/>
       <c r="G296"/>
@@ -11652,7 +11681,7 @@
       <c r="K296"/>
       <c r="L296"/>
     </row>
-    <row r="297" spans="5:12" ht="18.75">
+    <row r="297" spans="5:12" ht="18">
       <c r="E297"/>
       <c r="F297"/>
       <c r="G297"/>
@@ -11662,7 +11691,7 @@
       <c r="K297"/>
       <c r="L297"/>
     </row>
-    <row r="298" spans="5:12" ht="18.75">
+    <row r="298" spans="5:12" ht="18">
       <c r="E298"/>
       <c r="F298"/>
       <c r="G298"/>
@@ -11672,7 +11701,7 @@
       <c r="K298"/>
       <c r="L298"/>
     </row>
-    <row r="299" spans="5:12" ht="18.75">
+    <row r="299" spans="5:12" ht="18">
       <c r="E299"/>
       <c r="F299"/>
       <c r="G299"/>
@@ -11682,7 +11711,7 @@
       <c r="K299"/>
       <c r="L299"/>
     </row>
-    <row r="300" spans="5:12" ht="18.75">
+    <row r="300" spans="5:12" ht="18">
       <c r="E300"/>
       <c r="F300"/>
       <c r="G300"/>
@@ -11692,7 +11721,7 @@
       <c r="K300"/>
       <c r="L300"/>
     </row>
-    <row r="301" spans="5:12" ht="18.75">
+    <row r="301" spans="5:12" ht="18">
       <c r="E301"/>
       <c r="F301"/>
       <c r="G301"/>
@@ -11702,7 +11731,7 @@
       <c r="K301"/>
       <c r="L301"/>
     </row>
-    <row r="302" spans="5:12" ht="18.75">
+    <row r="302" spans="5:12" ht="18">
       <c r="E302"/>
       <c r="F302"/>
       <c r="G302"/>
@@ -11712,7 +11741,7 @@
       <c r="K302"/>
       <c r="L302"/>
     </row>
-    <row r="303" spans="5:12" ht="18.75">
+    <row r="303" spans="5:12" ht="18">
       <c r="E303"/>
       <c r="F303"/>
       <c r="G303"/>
@@ -11722,7 +11751,7 @@
       <c r="K303"/>
       <c r="L303"/>
     </row>
-    <row r="304" spans="5:12" ht="18.75">
+    <row r="304" spans="5:12" ht="18">
       <c r="E304"/>
       <c r="F304"/>
       <c r="G304"/>
@@ -11732,7 +11761,7 @@
       <c r="K304"/>
       <c r="L304"/>
     </row>
-    <row r="305" spans="5:12" ht="18.75">
+    <row r="305" spans="5:12" ht="18">
       <c r="E305"/>
       <c r="F305"/>
       <c r="G305"/>
@@ -11742,7 +11771,7 @@
       <c r="K305"/>
       <c r="L305"/>
     </row>
-    <row r="306" spans="5:12" ht="18.75">
+    <row r="306" spans="5:12" ht="18">
       <c r="E306"/>
       <c r="F306"/>
       <c r="G306"/>
@@ -11752,7 +11781,7 @@
       <c r="K306"/>
       <c r="L306"/>
     </row>
-    <row r="307" spans="5:12" ht="18.75">
+    <row r="307" spans="5:12" ht="18">
       <c r="E307"/>
       <c r="F307"/>
       <c r="G307"/>
@@ -11762,7 +11791,7 @@
       <c r="K307"/>
       <c r="L307"/>
     </row>
-    <row r="308" spans="5:12" ht="18.75">
+    <row r="308" spans="5:12" ht="18">
       <c r="E308"/>
       <c r="F308"/>
       <c r="G308"/>
@@ -11772,7 +11801,7 @@
       <c r="K308"/>
       <c r="L308"/>
     </row>
-    <row r="309" spans="5:12" ht="18.75">
+    <row r="309" spans="5:12" ht="18">
       <c r="E309"/>
       <c r="F309"/>
       <c r="G309"/>
@@ -11782,7 +11811,7 @@
       <c r="K309"/>
       <c r="L309"/>
     </row>
-    <row r="310" spans="5:12" ht="18.75">
+    <row r="310" spans="5:12" ht="18">
       <c r="E310"/>
       <c r="F310"/>
       <c r="G310"/>
@@ -11792,7 +11821,7 @@
       <c r="K310"/>
       <c r="L310"/>
     </row>
-    <row r="311" spans="5:12" ht="18.75">
+    <row r="311" spans="5:12" ht="18">
       <c r="E311"/>
       <c r="F311"/>
       <c r="G311"/>
@@ -11802,7 +11831,7 @@
       <c r="K311"/>
       <c r="L311"/>
     </row>
-    <row r="312" spans="5:12" ht="18.75">
+    <row r="312" spans="5:12" ht="18">
       <c r="E312"/>
       <c r="F312"/>
       <c r="G312"/>
@@ -11812,7 +11841,7 @@
       <c r="K312"/>
       <c r="L312"/>
     </row>
-    <row r="313" spans="5:12" ht="18.75">
+    <row r="313" spans="5:12" ht="18">
       <c r="E313"/>
       <c r="F313"/>
       <c r="G313"/>
@@ -11822,7 +11851,7 @@
       <c r="K313"/>
       <c r="L313"/>
     </row>
-    <row r="314" spans="5:12" ht="18.75">
+    <row r="314" spans="5:12" ht="18">
       <c r="E314"/>
       <c r="F314"/>
       <c r="G314"/>
@@ -11832,7 +11861,7 @@
       <c r="K314"/>
       <c r="L314"/>
     </row>
-    <row r="315" spans="5:12" ht="18.75">
+    <row r="315" spans="5:12" ht="18">
       <c r="E315"/>
       <c r="F315"/>
       <c r="G315"/>
@@ -11842,7 +11871,7 @@
       <c r="K315"/>
       <c r="L315"/>
     </row>
-    <row r="316" spans="5:12" ht="18.75">
+    <row r="316" spans="5:12" ht="18">
       <c r="E316"/>
       <c r="F316"/>
       <c r="G316"/>
@@ -11852,7 +11881,7 @@
       <c r="K316"/>
       <c r="L316"/>
     </row>
-    <row r="317" spans="5:12" ht="18.75">
+    <row r="317" spans="5:12" ht="18">
       <c r="E317"/>
       <c r="F317"/>
       <c r="G317"/>
@@ -11862,7 +11891,7 @@
       <c r="K317"/>
       <c r="L317"/>
     </row>
-    <row r="318" spans="5:12" ht="18.75">
+    <row r="318" spans="5:12" ht="18">
       <c r="E318"/>
       <c r="F318"/>
       <c r="G318"/>
@@ -11872,7 +11901,7 @@
       <c r="K318"/>
       <c r="L318"/>
     </row>
-    <row r="319" spans="5:12" ht="18.75">
+    <row r="319" spans="5:12" ht="18">
       <c r="E319"/>
       <c r="F319"/>
       <c r="G319"/>
@@ -11882,7 +11911,7 @@
       <c r="K319"/>
       <c r="L319"/>
     </row>
-    <row r="320" spans="5:12" ht="18.75">
+    <row r="320" spans="5:12" ht="18">
       <c r="E320"/>
       <c r="F320"/>
       <c r="G320"/>
@@ -11892,7 +11921,7 @@
       <c r="K320"/>
       <c r="L320"/>
     </row>
-    <row r="321" spans="5:12" ht="18.75">
+    <row r="321" spans="5:12" ht="18">
       <c r="E321"/>
       <c r="F321"/>
       <c r="G321"/>
@@ -11902,7 +11931,7 @@
       <c r="K321"/>
       <c r="L321"/>
     </row>
-    <row r="322" spans="5:12" ht="18.75">
+    <row r="322" spans="5:12" ht="18">
       <c r="E322"/>
       <c r="F322"/>
       <c r="G322"/>
@@ -11912,7 +11941,7 @@
       <c r="K322"/>
       <c r="L322"/>
     </row>
-    <row r="323" spans="5:12" ht="18.75">
+    <row r="323" spans="5:12" ht="18">
       <c r="E323"/>
       <c r="F323"/>
       <c r="G323"/>
@@ -11922,7 +11951,7 @@
       <c r="K323"/>
       <c r="L323"/>
     </row>
-    <row r="324" spans="5:12" ht="18.75">
+    <row r="324" spans="5:12" ht="18">
       <c r="E324"/>
       <c r="F324"/>
       <c r="G324"/>
@@ -11932,7 +11961,7 @@
       <c r="K324"/>
       <c r="L324"/>
     </row>
-    <row r="325" spans="5:12" ht="18.75">
+    <row r="325" spans="5:12" ht="18">
       <c r="E325"/>
       <c r="F325"/>
       <c r="G325"/>
@@ -11942,7 +11971,7 @@
       <c r="K325"/>
       <c r="L325"/>
     </row>
-    <row r="326" spans="5:12" ht="18.75">
+    <row r="326" spans="5:12" ht="18">
       <c r="E326"/>
       <c r="F326"/>
       <c r="G326"/>
@@ -11952,7 +11981,7 @@
       <c r="K326"/>
       <c r="L326"/>
     </row>
-    <row r="327" spans="5:12" ht="18.75">
+    <row r="327" spans="5:12" ht="18">
       <c r="E327"/>
       <c r="F327"/>
       <c r="G327"/>
@@ -11962,7 +11991,7 @@
       <c r="K327"/>
       <c r="L327"/>
     </row>
-    <row r="328" spans="5:12" ht="18.75">
+    <row r="328" spans="5:12" ht="18">
       <c r="E328"/>
       <c r="F328"/>
       <c r="G328"/>
@@ -11972,7 +12001,7 @@
       <c r="K328"/>
       <c r="L328"/>
     </row>
-    <row r="329" spans="5:12" ht="18.75">
+    <row r="329" spans="5:12" ht="18">
       <c r="E329"/>
       <c r="F329"/>
       <c r="G329"/>
@@ -11982,7 +12011,7 @@
       <c r="K329"/>
       <c r="L329"/>
     </row>
-    <row r="330" spans="5:12" ht="18.75">
+    <row r="330" spans="5:12" ht="18">
       <c r="E330"/>
       <c r="F330"/>
       <c r="G330"/>
@@ -11992,7 +12021,7 @@
       <c r="K330"/>
       <c r="L330"/>
     </row>
-    <row r="331" spans="5:12" ht="18.75">
+    <row r="331" spans="5:12" ht="18">
       <c r="E331"/>
       <c r="F331"/>
       <c r="G331"/>
@@ -12002,7 +12031,7 @@
       <c r="K331"/>
       <c r="L331"/>
     </row>
-    <row r="332" spans="5:12" ht="18.75">
+    <row r="332" spans="5:12" ht="18">
       <c r="E332"/>
       <c r="F332"/>
       <c r="G332"/>
@@ -12012,7 +12041,7 @@
       <c r="K332"/>
       <c r="L332"/>
     </row>
-    <row r="333" spans="5:12" ht="18.75">
+    <row r="333" spans="5:12" ht="18">
       <c r="E333"/>
       <c r="F333"/>
       <c r="G333"/>
@@ -12022,7 +12051,7 @@
       <c r="K333"/>
       <c r="L333"/>
     </row>
-    <row r="334" spans="5:12" ht="18.75">
+    <row r="334" spans="5:12" ht="18">
       <c r="E334"/>
       <c r="F334"/>
       <c r="G334"/>
@@ -12032,7 +12061,7 @@
       <c r="K334"/>
       <c r="L334"/>
     </row>
-    <row r="335" spans="5:12" ht="18.75">
+    <row r="335" spans="5:12" ht="18">
       <c r="E335"/>
       <c r="F335"/>
       <c r="G335"/>
@@ -12042,7 +12071,7 @@
       <c r="K335"/>
       <c r="L335"/>
     </row>
-    <row r="336" spans="5:12" ht="18.75">
+    <row r="336" spans="5:12" ht="18">
       <c r="E336"/>
       <c r="F336"/>
       <c r="G336"/>
@@ -12052,7 +12081,7 @@
       <c r="K336"/>
       <c r="L336"/>
     </row>
-    <row r="337" spans="5:12" ht="18.75">
+    <row r="337" spans="5:12" ht="18">
       <c r="E337"/>
       <c r="F337"/>
       <c r="G337"/>
@@ -12062,7 +12091,7 @@
       <c r="K337"/>
       <c r="L337"/>
     </row>
-    <row r="338" spans="5:12" ht="18.75">
+    <row r="338" spans="5:12" ht="18">
       <c r="E338"/>
       <c r="F338"/>
       <c r="G338"/>
@@ -12072,7 +12101,7 @@
       <c r="K338"/>
       <c r="L338"/>
     </row>
-    <row r="339" spans="5:12" ht="18.75">
+    <row r="339" spans="5:12" ht="18">
       <c r="E339"/>
       <c r="F339"/>
       <c r="G339"/>
@@ -12082,7 +12111,7 @@
       <c r="K339"/>
       <c r="L339"/>
     </row>
-    <row r="340" spans="5:12" ht="18.75">
+    <row r="340" spans="5:12" ht="18">
       <c r="E340"/>
       <c r="F340"/>
       <c r="G340"/>
@@ -12092,7 +12121,7 @@
       <c r="K340"/>
       <c r="L340"/>
     </row>
-    <row r="341" spans="5:12" ht="18.75">
+    <row r="341" spans="5:12" ht="18">
       <c r="E341"/>
       <c r="F341"/>
       <c r="G341"/>
@@ -12102,7 +12131,7 @@
       <c r="K341"/>
       <c r="L341"/>
     </row>
-    <row r="342" spans="5:12" ht="18.75">
+    <row r="342" spans="5:12" ht="18">
       <c r="E342"/>
       <c r="F342"/>
       <c r="G342"/>
@@ -12112,7 +12141,7 @@
       <c r="K342"/>
       <c r="L342"/>
     </row>
-    <row r="343" spans="5:12" ht="18.75">
+    <row r="343" spans="5:12" ht="18">
       <c r="E343"/>
       <c r="F343"/>
       <c r="G343"/>
@@ -12122,7 +12151,7 @@
       <c r="K343"/>
       <c r="L343"/>
     </row>
-    <row r="344" spans="5:12" ht="18.75">
+    <row r="344" spans="5:12" ht="18">
       <c r="E344"/>
       <c r="F344"/>
       <c r="G344"/>
@@ -12132,7 +12161,7 @@
       <c r="K344"/>
       <c r="L344"/>
     </row>
-    <row r="345" spans="5:12" ht="18.75">
+    <row r="345" spans="5:12" ht="18">
       <c r="E345"/>
       <c r="F345"/>
       <c r="G345"/>
@@ -12142,7 +12171,7 @@
       <c r="K345"/>
       <c r="L345"/>
     </row>
-    <row r="346" spans="5:12" ht="18.75">
+    <row r="346" spans="5:12" ht="18">
       <c r="E346"/>
       <c r="F346"/>
       <c r="G346"/>
@@ -12152,7 +12181,7 @@
       <c r="K346"/>
       <c r="L346"/>
     </row>
-    <row r="347" spans="5:12" ht="18.75">
+    <row r="347" spans="5:12" ht="18">
       <c r="E347"/>
       <c r="F347"/>
       <c r="G347"/>
@@ -12162,7 +12191,7 @@
       <c r="K347"/>
       <c r="L347"/>
     </row>
-    <row r="348" spans="5:12" ht="18.75">
+    <row r="348" spans="5:12" ht="18">
       <c r="E348"/>
       <c r="F348"/>
       <c r="G348"/>
@@ -12172,7 +12201,7 @@
       <c r="K348"/>
       <c r="L348"/>
     </row>
-    <row r="349" spans="5:12" ht="18.75">
+    <row r="349" spans="5:12" ht="18">
       <c r="E349"/>
       <c r="F349"/>
       <c r="G349"/>
@@ -12182,7 +12211,7 @@
       <c r="K349"/>
       <c r="L349"/>
     </row>
-    <row r="350" spans="5:12" ht="18.75">
+    <row r="350" spans="5:12" ht="18">
       <c r="E350"/>
       <c r="F350"/>
       <c r="G350"/>
@@ -12192,7 +12221,7 @@
       <c r="K350"/>
       <c r="L350"/>
     </row>
-    <row r="351" spans="5:12" ht="18.75">
+    <row r="351" spans="5:12" ht="18">
       <c r="E351"/>
       <c r="F351"/>
       <c r="G351"/>
@@ -12202,7 +12231,7 @@
       <c r="K351"/>
       <c r="L351"/>
     </row>
-    <row r="352" spans="5:12" ht="18.75">
+    <row r="352" spans="5:12" ht="18">
       <c r="E352"/>
       <c r="F352"/>
       <c r="G352"/>
@@ -12212,7 +12241,7 @@
       <c r="K352"/>
       <c r="L352"/>
     </row>
-    <row r="353" spans="5:12" ht="18.75">
+    <row r="353" spans="5:12" ht="18">
       <c r="E353"/>
       <c r="F353"/>
       <c r="G353"/>
@@ -12222,7 +12251,7 @@
       <c r="K353"/>
       <c r="L353"/>
     </row>
-    <row r="354" spans="5:12" ht="18.75">
+    <row r="354" spans="5:12" ht="18">
       <c r="E354"/>
       <c r="F354"/>
       <c r="G354"/>
@@ -12232,7 +12261,7 @@
       <c r="K354"/>
       <c r="L354"/>
     </row>
-    <row r="355" spans="5:12" ht="18.75">
+    <row r="355" spans="5:12" ht="18">
       <c r="E355"/>
       <c r="F355"/>
       <c r="G355"/>
@@ -12242,7 +12271,7 @@
       <c r="K355"/>
       <c r="L355"/>
     </row>
-    <row r="356" spans="5:12" ht="18.75">
+    <row r="356" spans="5:12" ht="18">
       <c r="E356"/>
       <c r="F356"/>
       <c r="G356"/>
@@ -12252,7 +12281,7 @@
       <c r="K356"/>
       <c r="L356"/>
     </row>
-    <row r="357" spans="5:12" ht="18.75">
+    <row r="357" spans="5:12" ht="18">
       <c r="E357"/>
       <c r="F357"/>
       <c r="G357"/>
@@ -12262,7 +12291,7 @@
       <c r="K357"/>
       <c r="L357"/>
     </row>
-    <row r="358" spans="5:12" ht="18.75">
+    <row r="358" spans="5:12" ht="18">
       <c r="E358"/>
       <c r="F358"/>
       <c r="G358"/>
@@ -12272,7 +12301,7 @@
       <c r="K358"/>
       <c r="L358"/>
     </row>
-    <row r="359" spans="5:12" ht="18.75">
+    <row r="359" spans="5:12" ht="18">
       <c r="E359"/>
       <c r="F359"/>
       <c r="G359"/>
@@ -12282,7 +12311,7 @@
       <c r="K359"/>
       <c r="L359"/>
     </row>
-    <row r="360" spans="5:12" ht="18.75">
+    <row r="360" spans="5:12" ht="18">
       <c r="E360"/>
       <c r="F360"/>
       <c r="G360"/>
@@ -12292,7 +12321,7 @@
       <c r="K360"/>
       <c r="L360"/>
     </row>
-    <row r="361" spans="5:12" ht="18.75">
+    <row r="361" spans="5:12" ht="18">
       <c r="E361"/>
       <c r="F361"/>
       <c r="G361"/>
@@ -12302,7 +12331,7 @@
       <c r="K361"/>
       <c r="L361"/>
     </row>
-    <row r="362" spans="5:12" ht="18.75">
+    <row r="362" spans="5:12" ht="18">
       <c r="E362"/>
       <c r="F362"/>
       <c r="G362"/>
@@ -12312,7 +12341,7 @@
       <c r="K362"/>
       <c r="L362"/>
     </row>
-    <row r="363" spans="5:12" ht="18.75">
+    <row r="363" spans="5:12" ht="18">
       <c r="E363"/>
       <c r="F363"/>
       <c r="G363"/>
@@ -12322,7 +12351,7 @@
       <c r="K363"/>
       <c r="L363"/>
     </row>
-    <row r="364" spans="5:12" ht="18.75">
+    <row r="364" spans="5:12" ht="18">
       <c r="E364"/>
       <c r="F364"/>
       <c r="G364"/>
@@ -12332,7 +12361,7 @@
       <c r="K364"/>
       <c r="L364"/>
     </row>
-    <row r="365" spans="5:12" ht="18.75">
+    <row r="365" spans="5:12" ht="18">
       <c r="E365"/>
       <c r="F365"/>
       <c r="G365"/>
@@ -12342,7 +12371,7 @@
       <c r="K365"/>
       <c r="L365"/>
     </row>
-    <row r="366" spans="5:12" ht="18.75">
+    <row r="366" spans="5:12" ht="18">
       <c r="E366"/>
       <c r="F366"/>
       <c r="G366"/>
@@ -12352,7 +12381,7 @@
       <c r="K366"/>
       <c r="L366"/>
     </row>
-    <row r="367" spans="5:12" ht="18.75">
+    <row r="367" spans="5:12" ht="18">
       <c r="E367"/>
       <c r="F367"/>
       <c r="G367"/>
@@ -12362,7 +12391,7 @@
       <c r="K367"/>
       <c r="L367"/>
     </row>
-    <row r="368" spans="5:12" ht="18.75">
+    <row r="368" spans="5:12" ht="18">
       <c r="E368"/>
       <c r="F368"/>
       <c r="G368"/>
@@ -12372,7 +12401,7 @@
       <c r="K368"/>
       <c r="L368"/>
     </row>
-    <row r="369" spans="5:12" ht="18.75">
+    <row r="369" spans="5:12" ht="18">
       <c r="E369"/>
       <c r="F369"/>
       <c r="G369"/>
@@ -12382,7 +12411,7 @@
       <c r="K369"/>
       <c r="L369"/>
     </row>
-    <row r="370" spans="5:12" ht="18.75">
+    <row r="370" spans="5:12" ht="18">
       <c r="E370"/>
       <c r="F370"/>
       <c r="G370"/>
@@ -12392,7 +12421,7 @@
       <c r="K370"/>
       <c r="L370"/>
     </row>
-    <row r="371" spans="5:12" ht="18.75">
+    <row r="371" spans="5:12" ht="18">
       <c r="E371"/>
       <c r="F371"/>
       <c r="G371"/>
@@ -12402,7 +12431,7 @@
       <c r="K371"/>
       <c r="L371"/>
     </row>
-    <row r="372" spans="5:12" ht="18.75">
+    <row r="372" spans="5:12" ht="18">
       <c r="E372"/>
       <c r="F372"/>
       <c r="G372"/>
@@ -12412,7 +12441,7 @@
       <c r="K372"/>
       <c r="L372"/>
     </row>
-    <row r="373" spans="5:12" ht="18.75">
+    <row r="373" spans="5:12" ht="18">
       <c r="E373"/>
       <c r="F373"/>
       <c r="G373"/>
@@ -12422,7 +12451,7 @@
       <c r="K373"/>
       <c r="L373"/>
     </row>
-    <row r="374" spans="5:12" ht="18.75">
+    <row r="374" spans="5:12" ht="18">
       <c r="E374"/>
       <c r="F374"/>
       <c r="G374"/>
@@ -12432,7 +12461,7 @@
       <c r="K374"/>
       <c r="L374"/>
     </row>
-    <row r="375" spans="5:12" ht="18.75">
+    <row r="375" spans="5:12" ht="18">
       <c r="E375"/>
       <c r="F375"/>
       <c r="G375"/>
@@ -12442,7 +12471,7 @@
       <c r="K375"/>
       <c r="L375"/>
     </row>
-    <row r="376" spans="5:12" ht="18.75">
+    <row r="376" spans="5:12" ht="18">
       <c r="E376"/>
       <c r="F376"/>
       <c r="G376"/>
@@ -12452,7 +12481,7 @@
       <c r="K376"/>
       <c r="L376"/>
     </row>
-    <row r="377" spans="5:12" ht="18.75">
+    <row r="377" spans="5:12" ht="18">
       <c r="E377"/>
       <c r="F377"/>
       <c r="G377"/>
@@ -12462,7 +12491,7 @@
       <c r="K377"/>
       <c r="L377"/>
     </row>
-    <row r="378" spans="5:12" ht="18.75">
+    <row r="378" spans="5:12" ht="18">
       <c r="E378"/>
       <c r="F378"/>
       <c r="G378"/>
@@ -12472,7 +12501,7 @@
       <c r="K378"/>
       <c r="L378"/>
     </row>
-    <row r="379" spans="5:12" ht="18.75">
+    <row r="379" spans="5:12" ht="18">
       <c r="E379"/>
       <c r="F379"/>
       <c r="G379"/>
@@ -12482,7 +12511,7 @@
       <c r="K379"/>
       <c r="L379"/>
     </row>
-    <row r="380" spans="5:12" ht="18.75">
+    <row r="380" spans="5:12" ht="18">
       <c r="E380"/>
       <c r="F380"/>
       <c r="G380"/>
@@ -12492,7 +12521,7 @@
       <c r="K380"/>
       <c r="L380"/>
     </row>
-    <row r="381" spans="5:12" ht="18.75">
+    <row r="381" spans="5:12" ht="18">
       <c r="E381"/>
       <c r="F381"/>
       <c r="G381"/>
@@ -12502,7 +12531,7 @@
       <c r="K381"/>
       <c r="L381"/>
     </row>
-    <row r="382" spans="5:12" ht="18.75">
+    <row r="382" spans="5:12" ht="18">
       <c r="E382"/>
       <c r="F382"/>
       <c r="G382"/>
@@ -12512,7 +12541,7 @@
       <c r="K382"/>
       <c r="L382"/>
     </row>
-    <row r="383" spans="5:12" ht="18.75">
+    <row r="383" spans="5:12" ht="18">
       <c r="E383"/>
       <c r="F383"/>
       <c r="G383"/>
@@ -12522,7 +12551,7 @@
       <c r="K383"/>
       <c r="L383"/>
     </row>
-    <row r="384" spans="5:12" ht="18.75">
+    <row r="384" spans="5:12" ht="18">
       <c r="E384"/>
       <c r="F384"/>
       <c r="G384"/>
@@ -12532,7 +12561,7 @@
       <c r="K384"/>
       <c r="L384"/>
     </row>
-    <row r="385" spans="5:12" ht="18.75">
+    <row r="385" spans="5:12" ht="18">
       <c r="E385"/>
       <c r="F385"/>
       <c r="G385"/>
@@ -12542,7 +12571,7 @@
       <c r="K385"/>
       <c r="L385"/>
     </row>
-    <row r="386" spans="5:12" ht="18.75">
+    <row r="386" spans="5:12" ht="18">
       <c r="E386"/>
       <c r="F386"/>
       <c r="G386"/>
@@ -12552,7 +12581,7 @@
       <c r="K386"/>
       <c r="L386"/>
     </row>
-    <row r="387" spans="5:12" ht="18.75">
+    <row r="387" spans="5:12" ht="18">
       <c r="E387"/>
       <c r="F387"/>
       <c r="G387"/>
@@ -12562,7 +12591,7 @@
       <c r="K387"/>
       <c r="L387"/>
     </row>
-    <row r="388" spans="5:12" ht="18.75">
+    <row r="388" spans="5:12" ht="18">
       <c r="E388"/>
       <c r="F388"/>
       <c r="G388"/>
@@ -12572,7 +12601,7 @@
       <c r="K388"/>
       <c r="L388"/>
     </row>
-    <row r="389" spans="5:12" ht="18.75">
+    <row r="389" spans="5:12" ht="18">
       <c r="E389"/>
       <c r="F389"/>
       <c r="G389"/>
@@ -12582,7 +12611,7 @@
       <c r="K389"/>
       <c r="L389"/>
     </row>
-    <row r="390" spans="5:12" ht="18.75">
+    <row r="390" spans="5:12" ht="18">
       <c r="E390"/>
       <c r="F390"/>
       <c r="G390"/>
@@ -12592,7 +12621,7 @@
       <c r="K390"/>
       <c r="L390"/>
     </row>
-    <row r="391" spans="5:12" ht="18.75">
+    <row r="391" spans="5:12" ht="18">
       <c r="E391"/>
       <c r="F391"/>
       <c r="G391"/>
@@ -12602,7 +12631,7 @@
       <c r="K391"/>
       <c r="L391"/>
     </row>
-    <row r="392" spans="5:12" ht="18.75">
+    <row r="392" spans="5:12" ht="18">
       <c r="E392"/>
       <c r="F392"/>
       <c r="G392"/>
@@ -12612,7 +12641,7 @@
       <c r="K392"/>
       <c r="L392"/>
     </row>
-    <row r="393" spans="5:12" ht="18.75">
+    <row r="393" spans="5:12" ht="18">
       <c r="E393"/>
       <c r="F393"/>
       <c r="G393"/>
@@ -12622,7 +12651,7 @@
       <c r="K393"/>
       <c r="L393"/>
     </row>
-    <row r="394" spans="5:12" ht="18.75">
+    <row r="394" spans="5:12" ht="18">
       <c r="E394"/>
       <c r="F394"/>
       <c r="G394"/>
@@ -12632,7 +12661,7 @@
       <c r="K394"/>
       <c r="L394"/>
     </row>
-    <row r="395" spans="5:12" ht="18.75">
+    <row r="395" spans="5:12" ht="18">
       <c r="E395"/>
       <c r="F395"/>
       <c r="G395"/>
@@ -12642,7 +12671,7 @@
       <c r="K395"/>
       <c r="L395"/>
     </row>
-    <row r="396" spans="5:12" ht="18.75">
+    <row r="396" spans="5:12" ht="18">
       <c r="E396"/>
       <c r="F396"/>
       <c r="G396"/>
@@ -12652,7 +12681,7 @@
       <c r="K396"/>
       <c r="L396"/>
     </row>
-    <row r="397" spans="5:12" ht="18.75">
+    <row r="397" spans="5:12" ht="18">
       <c r="E397"/>
       <c r="F397"/>
       <c r="G397"/>
@@ -12662,7 +12691,7 @@
       <c r="K397"/>
       <c r="L397"/>
     </row>
-    <row r="398" spans="5:12" ht="18.75">
+    <row r="398" spans="5:12" ht="18">
       <c r="E398"/>
       <c r="F398"/>
       <c r="G398"/>
@@ -12672,7 +12701,7 @@
       <c r="K398"/>
       <c r="L398"/>
     </row>
-    <row r="399" spans="5:12" ht="18.75">
+    <row r="399" spans="5:12" ht="18">
       <c r="E399"/>
       <c r="F399"/>
       <c r="G399"/>
@@ -12682,7 +12711,7 @@
       <c r="K399"/>
       <c r="L399"/>
     </row>
-    <row r="400" spans="5:12" ht="18.75">
+    <row r="400" spans="5:12" ht="18">
       <c r="E400"/>
       <c r="F400"/>
       <c r="G400"/>
@@ -12692,7 +12721,7 @@
       <c r="K400"/>
       <c r="L400"/>
     </row>
-    <row r="401" spans="5:12" ht="18.75">
+    <row r="401" spans="5:12" ht="18">
       <c r="E401"/>
       <c r="F401"/>
       <c r="G401"/>
@@ -12702,7 +12731,7 @@
       <c r="K401"/>
       <c r="L401"/>
     </row>
-    <row r="402" spans="5:12" ht="18.75">
+    <row r="402" spans="5:12" ht="18">
       <c r="E402"/>
       <c r="F402"/>
       <c r="G402"/>
@@ -12712,7 +12741,7 @@
       <c r="K402"/>
       <c r="L402"/>
     </row>
-    <row r="403" spans="5:12" ht="18.75">
+    <row r="403" spans="5:12" ht="18">
       <c r="E403"/>
       <c r="F403"/>
       <c r="G403"/>
@@ -12722,7 +12751,7 @@
       <c r="K403"/>
       <c r="L403"/>
     </row>
-    <row r="404" spans="5:12" ht="18.75">
+    <row r="404" spans="5:12" ht="18">
       <c r="E404"/>
       <c r="F404"/>
       <c r="G404"/>
@@ -12732,7 +12761,7 @@
       <c r="K404"/>
       <c r="L404"/>
     </row>
-    <row r="405" spans="5:12" ht="18.75">
+    <row r="405" spans="5:12" ht="18">
       <c r="E405"/>
       <c r="F405"/>
       <c r="G405"/>
@@ -12742,7 +12771,7 @@
       <c r="K405"/>
       <c r="L405"/>
     </row>
-    <row r="406" spans="5:12" ht="18.75">
+    <row r="406" spans="5:12" ht="18">
       <c r="E406"/>
       <c r="F406"/>
       <c r="G406"/>
@@ -12752,7 +12781,7 @@
       <c r="K406"/>
       <c r="L406"/>
     </row>
-    <row r="407" spans="5:12" ht="18.75">
+    <row r="407" spans="5:12" ht="18">
       <c r="E407"/>
       <c r="F407"/>
       <c r="G407"/>
@@ -12762,7 +12791,7 @@
       <c r="K407"/>
       <c r="L407"/>
     </row>
-    <row r="408" spans="5:12" ht="18.75">
+    <row r="408" spans="5:12" ht="18">
       <c r="E408"/>
       <c r="F408"/>
       <c r="G408"/>
@@ -12772,7 +12801,7 @@
       <c r="K408"/>
       <c r="L408"/>
     </row>
-    <row r="409" spans="5:12" ht="18.75">
+    <row r="409" spans="5:12" ht="18">
       <c r="E409"/>
       <c r="F409"/>
       <c r="G409"/>
@@ -12782,7 +12811,7 @@
       <c r="K409"/>
       <c r="L409"/>
     </row>
-    <row r="410" spans="5:12" ht="18.75">
+    <row r="410" spans="5:12" ht="18">
       <c r="E410"/>
       <c r="F410"/>
       <c r="G410"/>
@@ -12792,7 +12821,7 @@
       <c r="K410"/>
       <c r="L410"/>
     </row>
-    <row r="411" spans="5:12" ht="18.75">
+    <row r="411" spans="5:12" ht="18">
       <c r="E411"/>
       <c r="F411"/>
       <c r="G411"/>
@@ -12802,7 +12831,7 @@
       <c r="K411"/>
       <c r="L411"/>
     </row>
-    <row r="412" spans="5:12" ht="18.75">
+    <row r="412" spans="5:12" ht="18">
       <c r="E412"/>
       <c r="F412"/>
       <c r="G412"/>
@@ -12812,7 +12841,7 @@
       <c r="K412"/>
       <c r="L412"/>
     </row>
-    <row r="413" spans="5:12" ht="18.75">
+    <row r="413" spans="5:12" ht="18">
       <c r="E413"/>
       <c r="F413"/>
       <c r="G413"/>
@@ -12822,7 +12851,7 @@
       <c r="K413"/>
       <c r="L413"/>
     </row>
-    <row r="414" spans="5:12" ht="18.75">
+    <row r="414" spans="5:12" ht="18">
       <c r="E414"/>
       <c r="F414"/>
       <c r="G414"/>
@@ -12832,7 +12861,7 @@
       <c r="K414"/>
       <c r="L414"/>
     </row>
-    <row r="415" spans="5:12" ht="18.75">
+    <row r="415" spans="5:12" ht="18">
       <c r="E415"/>
       <c r="F415"/>
       <c r="G415"/>
@@ -12842,7 +12871,7 @@
       <c r="K415"/>
       <c r="L415"/>
     </row>
-    <row r="416" spans="5:12" ht="18.75">
+    <row r="416" spans="5:12" ht="18">
       <c r="E416"/>
       <c r="F416"/>
       <c r="G416"/>
@@ -12852,7 +12881,7 @@
       <c r="K416"/>
       <c r="L416"/>
     </row>
-    <row r="417" spans="5:12" ht="18.75">
+    <row r="417" spans="5:12" ht="18">
       <c r="E417"/>
       <c r="F417"/>
       <c r="G417"/>
@@ -12862,7 +12891,7 @@
       <c r="K417"/>
       <c r="L417"/>
     </row>
-    <row r="418" spans="5:12" ht="18.75">
+    <row r="418" spans="5:12" ht="18">
       <c r="E418"/>
       <c r="F418"/>
       <c r="G418"/>
@@ -12872,7 +12901,7 @@
       <c r="K418"/>
       <c r="L418"/>
     </row>
-    <row r="419" spans="5:12" ht="18.75">
+    <row r="419" spans="5:12" ht="18">
       <c r="E419"/>
       <c r="F419"/>
       <c r="G419"/>
@@ -12882,7 +12911,7 @@
       <c r="K419"/>
       <c r="L419"/>
     </row>
-    <row r="420" spans="5:12" ht="18.75">
+    <row r="420" spans="5:12" ht="18">
       <c r="E420"/>
       <c r="F420"/>
       <c r="G420"/>
@@ -12892,7 +12921,7 @@
       <c r="K420"/>
       <c r="L420"/>
     </row>
-    <row r="421" spans="5:12" ht="18.75">
+    <row r="421" spans="5:12" ht="18">
       <c r="E421"/>
       <c r="F421"/>
       <c r="G421"/>
@@ -12902,7 +12931,7 @@
       <c r="K421"/>
       <c r="L421"/>
     </row>
-    <row r="422" spans="5:12" ht="18.75">
+    <row r="422" spans="5:12" ht="18">
       <c r="E422"/>
       <c r="F422"/>
       <c r="G422"/>
@@ -12912,7 +12941,7 @@
       <c r="K422"/>
       <c r="L422"/>
     </row>
-    <row r="423" spans="5:12" ht="18.75">
+    <row r="423" spans="5:12" ht="18">
       <c r="E423"/>
       <c r="F423"/>
       <c r="G423"/>
@@ -12922,7 +12951,7 @@
       <c r="K423"/>
       <c r="L423"/>
     </row>
-    <row r="424" spans="5:12" ht="18.75">
+    <row r="424" spans="5:12" ht="18">
       <c r="E424"/>
       <c r="F424"/>
       <c r="G424"/>
@@ -12932,7 +12961,7 @@
       <c r="K424"/>
       <c r="L424"/>
     </row>
-    <row r="425" spans="5:12" ht="18.75">
+    <row r="425" spans="5:12" ht="18">
       <c r="E425"/>
       <c r="F425"/>
       <c r="G425"/>
@@ -12942,7 +12971,7 @@
       <c r="K425"/>
       <c r="L425"/>
     </row>
-    <row r="426" spans="5:12" ht="18.75">
+    <row r="426" spans="5:12" ht="18">
       <c r="E426"/>
       <c r="F426"/>
       <c r="G426"/>
@@ -12952,7 +12981,7 @@
       <c r="K426"/>
       <c r="L426"/>
     </row>
-    <row r="427" spans="5:12" ht="18.75">
+    <row r="427" spans="5:12" ht="18">
       <c r="E427"/>
       <c r="F427"/>
       <c r="G427"/>
@@ -12962,7 +12991,7 @@
       <c r="K427"/>
       <c r="L427"/>
     </row>
-    <row r="428" spans="5:12" ht="18.75">
+    <row r="428" spans="5:12" ht="18">
       <c r="E428"/>
       <c r="F428"/>
       <c r="G428"/>
@@ -12972,7 +13001,7 @@
       <c r="K428"/>
       <c r="L428"/>
     </row>
-    <row r="429" spans="5:12" ht="18.75">
+    <row r="429" spans="5:12" ht="18">
       <c r="E429"/>
       <c r="F429"/>
       <c r="G429"/>
@@ -12982,7 +13011,7 @@
       <c r="K429"/>
       <c r="L429"/>
     </row>
-    <row r="430" spans="5:12" ht="18.75">
+    <row r="430" spans="5:12" ht="18">
       <c r="E430"/>
       <c r="F430"/>
       <c r="G430"/>
@@ -12992,7 +13021,7 @@
       <c r="K430"/>
       <c r="L430"/>
     </row>
-    <row r="431" spans="5:12" ht="18.75">
+    <row r="431" spans="5:12" ht="18">
       <c r="E431"/>
       <c r="F431"/>
       <c r="G431"/>
@@ -13002,7 +13031,7 @@
       <c r="K431"/>
       <c r="L431"/>
     </row>
-    <row r="432" spans="5:12" ht="18.75">
+    <row r="432" spans="5:12" ht="18">
       <c r="E432"/>
       <c r="F432"/>
       <c r="G432"/>
@@ -13012,7 +13041,7 @@
       <c r="K432"/>
       <c r="L432"/>
     </row>
-    <row r="433" spans="5:12" ht="18.75">
+    <row r="433" spans="5:12" ht="18">
       <c r="E433"/>
       <c r="F433"/>
       <c r="G433"/>
@@ -13022,7 +13051,7 @@
       <c r="K433"/>
       <c r="L433"/>
     </row>
-    <row r="434" spans="5:12" ht="18.75">
+    <row r="434" spans="5:12" ht="18">
       <c r="E434"/>
       <c r="F434"/>
       <c r="G434"/>
@@ -13032,7 +13061,7 @@
       <c r="K434"/>
       <c r="L434"/>
     </row>
-    <row r="435" spans="5:12" ht="18.75">
+    <row r="435" spans="5:12" ht="18">
       <c r="E435"/>
       <c r="F435"/>
       <c r="G435"/>
@@ -13042,7 +13071,7 @@
       <c r="K435"/>
       <c r="L435"/>
     </row>
-    <row r="436" spans="5:12" ht="18.75">
+    <row r="436" spans="5:12" ht="18">
       <c r="E436"/>
       <c r="F436"/>
       <c r="G436"/>
@@ -13052,7 +13081,7 @@
       <c r="K436"/>
       <c r="L436"/>
     </row>
-    <row r="437" spans="5:12" ht="18.75">
+    <row r="437" spans="5:12" ht="18">
       <c r="E437"/>
       <c r="F437"/>
       <c r="G437"/>
@@ -13062,7 +13091,7 @@
       <c r="K437"/>
       <c r="L437"/>
     </row>
-    <row r="438" spans="5:12" ht="18.75">
+    <row r="438" spans="5:12" ht="18">
       <c r="E438"/>
       <c r="F438"/>
       <c r="G438"/>
@@ -13072,7 +13101,7 @@
       <c r="K438"/>
       <c r="L438"/>
     </row>
-    <row r="439" spans="5:12" ht="18.75">
+    <row r="439" spans="5:12" ht="18">
       <c r="E439"/>
       <c r="F439"/>
       <c r="G439"/>
@@ -13082,7 +13111,7 @@
       <c r="K439"/>
       <c r="L439"/>
     </row>
-    <row r="440" spans="5:12" ht="18.75">
+    <row r="440" spans="5:12" ht="18">
       <c r="E440"/>
       <c r="F440"/>
       <c r="G440"/>
@@ -13092,7 +13121,7 @@
       <c r="K440"/>
       <c r="L440"/>
     </row>
-    <row r="441" spans="5:12" ht="18.75">
+    <row r="441" spans="5:12" ht="18">
       <c r="E441"/>
       <c r="F441"/>
       <c r="G441"/>
@@ -13102,7 +13131,7 @@
       <c r="K441"/>
       <c r="L441"/>
     </row>
-    <row r="442" spans="5:12" ht="18.75">
+    <row r="442" spans="5:12" ht="18">
       <c r="E442"/>
       <c r="F442"/>
       <c r="G442"/>
@@ -13112,7 +13141,7 @@
       <c r="K442"/>
       <c r="L442"/>
     </row>
-    <row r="443" spans="5:12" ht="18.75">
+    <row r="443" spans="5:12" ht="18">
       <c r="E443"/>
       <c r="F443"/>
       <c r="G443"/>
@@ -13122,7 +13151,7 @@
       <c r="K443"/>
       <c r="L443"/>
     </row>
-    <row r="444" spans="5:12" ht="18.75">
+    <row r="444" spans="5:12" ht="18">
       <c r="E444"/>
       <c r="F444"/>
       <c r="G444"/>
@@ -13132,7 +13161,7 @@
       <c r="K444"/>
       <c r="L444"/>
     </row>
-    <row r="445" spans="5:12" ht="18.75">
+    <row r="445" spans="5:12" ht="18">
       <c r="E445"/>
       <c r="F445"/>
       <c r="G445"/>
@@ -13142,7 +13171,7 @@
       <c r="K445"/>
       <c r="L445"/>
     </row>
-    <row r="446" spans="5:12" ht="18.75">
+    <row r="446" spans="5:12" ht="18">
       <c r="E446"/>
       <c r="F446"/>
       <c r="G446"/>
@@ -13152,7 +13181,7 @@
       <c r="K446"/>
       <c r="L446"/>
     </row>
-    <row r="447" spans="5:12" ht="18.75">
+    <row r="447" spans="5:12" ht="18">
       <c r="E447"/>
       <c r="F447"/>
       <c r="G447"/>
@@ -13162,7 +13191,7 @@
       <c r="K447"/>
       <c r="L447"/>
     </row>
-    <row r="448" spans="5:12" ht="18.75">
+    <row r="448" spans="5:12" ht="18">
       <c r="E448"/>
       <c r="F448"/>
       <c r="G448"/>
@@ -13172,7 +13201,7 @@
       <c r="K448"/>
       <c r="L448"/>
     </row>
-    <row r="449" spans="5:12" ht="18.75">
+    <row r="449" spans="5:12" ht="18">
       <c r="E449"/>
       <c r="F449"/>
       <c r="G449"/>
@@ -13182,7 +13211,7 @@
       <c r="K449"/>
       <c r="L449"/>
     </row>
-    <row r="450" spans="5:12" ht="18.75">
+    <row r="450" spans="5:12" ht="18">
       <c r="E450"/>
       <c r="F450"/>
       <c r="G450"/>
@@ -13192,7 +13221,7 @@
       <c r="K450"/>
       <c r="L450"/>
     </row>
-    <row r="451" spans="5:12" ht="18.75">
+    <row r="451" spans="5:12" ht="18">
       <c r="E451"/>
       <c r="F451"/>
       <c r="G451"/>
@@ -13202,7 +13231,7 @@
       <c r="K451"/>
       <c r="L451"/>
     </row>
-    <row r="452" spans="5:12" ht="18.75">
+    <row r="452" spans="5:12" ht="18">
       <c r="E452"/>
       <c r="F452"/>
       <c r="G452"/>
@@ -13212,7 +13241,7 @@
       <c r="K452"/>
       <c r="L452"/>
     </row>
-    <row r="453" spans="5:12" ht="18.75">
+    <row r="453" spans="5:12" ht="18">
       <c r="E453"/>
       <c r="F453"/>
       <c r="G453"/>
@@ -13222,7 +13251,7 @@
       <c r="K453"/>
       <c r="L453"/>
     </row>
-    <row r="454" spans="5:12" ht="18.75">
+    <row r="454" spans="5:12" ht="18">
       <c r="E454"/>
       <c r="F454"/>
       <c r="G454"/>
@@ -13232,7 +13261,7 @@
       <c r="K454"/>
       <c r="L454"/>
     </row>
-    <row r="455" spans="5:12" ht="18.75">
+    <row r="455" spans="5:12" ht="18">
       <c r="E455"/>
       <c r="F455"/>
       <c r="G455"/>
@@ -13242,7 +13271,7 @@
       <c r="K455"/>
       <c r="L455"/>
     </row>
-    <row r="456" spans="5:12" ht="18.75">
+    <row r="456" spans="5:12" ht="18">
       <c r="E456"/>
       <c r="F456"/>
       <c r="G456"/>
@@ -13252,7 +13281,7 @@
       <c r="K456"/>
       <c r="L456"/>
     </row>
-    <row r="457" spans="5:12" ht="18.75">
+    <row r="457" spans="5:12" ht="18">
       <c r="E457"/>
       <c r="F457"/>
       <c r="G457"/>
@@ -13262,7 +13291,7 @@
       <c r="K457"/>
       <c r="L457"/>
     </row>
-    <row r="458" spans="5:12" ht="18.75">
+    <row r="458" spans="5:12" ht="18">
       <c r="E458"/>
       <c r="F458"/>
       <c r="G458"/>
@@ -13272,7 +13301,7 @@
       <c r="K458"/>
       <c r="L458"/>
     </row>
-    <row r="459" spans="5:12" ht="18.75">
+    <row r="459" spans="5:12" ht="18">
       <c r="E459"/>
       <c r="F459"/>
       <c r="G459"/>
@@ -13282,7 +13311,7 @@
       <c r="K459"/>
       <c r="L459"/>
     </row>
-    <row r="460" spans="5:12" ht="18.75">
+    <row r="460" spans="5:12" ht="18">
       <c r="E460"/>
       <c r="F460"/>
       <c r="G460"/>
@@ -13292,7 +13321,7 @@
       <c r="K460"/>
       <c r="L460"/>
     </row>
-    <row r="461" spans="5:12" ht="18.75">
+    <row r="461" spans="5:12" ht="18">
       <c r="E461"/>
       <c r="F461"/>
       <c r="G461"/>
@@ -13302,7 +13331,7 @@
       <c r="K461"/>
       <c r="L461"/>
     </row>
-    <row r="462" spans="5:12" ht="18.75">
+    <row r="462" spans="5:12" ht="18">
       <c r="E462"/>
       <c r="F462"/>
       <c r="G462"/>
@@ -13312,7 +13341,7 @@
       <c r="K462"/>
       <c r="L462"/>
     </row>
-    <row r="463" spans="5:12" ht="18.75">
+    <row r="463" spans="5:12" ht="18">
       <c r="E463"/>
       <c r="F463"/>
       <c r="G463"/>
@@ -13322,7 +13351,7 @@
       <c r="K463"/>
       <c r="L463"/>
     </row>
-    <row r="464" spans="5:12" ht="18.75">
+    <row r="464" spans="5:12" ht="18">
       <c r="E464"/>
       <c r="F464"/>
       <c r="G464"/>
@@ -13332,7 +13361,7 @@
       <c r="K464"/>
       <c r="L464"/>
     </row>
-    <row r="465" spans="5:12" ht="18.75">
+    <row r="465" spans="5:12" ht="18">
       <c r="E465"/>
       <c r="F465"/>
       <c r="G465"/>
@@ -13342,7 +13371,7 @@
       <c r="K465"/>
       <c r="L465"/>
     </row>
-    <row r="466" spans="5:12" ht="18.75">
+    <row r="466" spans="5:12" ht="18">
       <c r="E466"/>
       <c r="F466"/>
       <c r="G466"/>
@@ -13352,7 +13381,7 @@
       <c r="K466"/>
       <c r="L466"/>
     </row>
-    <row r="467" spans="5:12" ht="18.75">
+    <row r="467" spans="5:12" ht="18">
       <c r="E467"/>
       <c r="F467"/>
       <c r="G467"/>
@@ -13362,7 +13391,7 @@
       <c r="K467"/>
       <c r="L467"/>
     </row>
-    <row r="468" spans="5:12" ht="18.75">
+    <row r="468" spans="5:12" ht="18">
       <c r="E468"/>
       <c r="F468"/>
       <c r="G468"/>
@@ -13372,7 +13401,7 @@
       <c r="K468"/>
       <c r="L468"/>
     </row>
-    <row r="469" spans="5:12" ht="18.75">
+    <row r="469" spans="5:12" ht="18">
       <c r="E469"/>
       <c r="F469"/>
       <c r="G469"/>
@@ -13382,7 +13411,7 @@
       <c r="K469"/>
       <c r="L469"/>
     </row>
-    <row r="470" spans="5:12" ht="18.75">
+    <row r="470" spans="5:12" ht="18">
       <c r="E470"/>
       <c r="F470"/>
       <c r="G470"/>
@@ -13392,7 +13421,7 @@
       <c r="K470"/>
       <c r="L470"/>
     </row>
-    <row r="471" spans="5:12" ht="18.75">
+    <row r="471" spans="5:12" ht="18">
       <c r="E471"/>
       <c r="F471"/>
       <c r="G471"/>
@@ -13402,7 +13431,7 @@
       <c r="K471"/>
       <c r="L471"/>
     </row>
-    <row r="472" spans="5:12" ht="18.75">
+    <row r="472" spans="5:12" ht="18">
       <c r="E472"/>
       <c r="F472"/>
       <c r="G472"/>
@@ -13412,7 +13441,7 @@
       <c r="K472"/>
       <c r="L472"/>
     </row>
-    <row r="473" spans="5:12" ht="18.75">
+    <row r="473" spans="5:12" ht="18">
       <c r="E473"/>
       <c r="F473"/>
       <c r="G473"/>
@@ -13422,7 +13451,7 @@
       <c r="K473"/>
       <c r="L473"/>
     </row>
-    <row r="474" spans="5:12" ht="18.75">
+    <row r="474" spans="5:12" ht="18">
       <c r="E474"/>
       <c r="F474"/>
       <c r="G474"/>
@@ -13432,7 +13461,7 @@
       <c r="K474"/>
       <c r="L474"/>
     </row>
-    <row r="475" spans="5:12" ht="18.75">
+    <row r="475" spans="5:12" ht="18">
       <c r="E475"/>
       <c r="F475"/>
       <c r="G475"/>
@@ -13442,7 +13471,7 @@
       <c r="K475"/>
       <c r="L475"/>
     </row>
-    <row r="476" spans="5:12" ht="18.75">
+    <row r="476" spans="5:12" ht="18">
       <c r="E476"/>
       <c r="F476"/>
       <c r="G476"/>
@@ -13452,7 +13481,7 @@
       <c r="K476"/>
       <c r="L476"/>
     </row>
-    <row r="477" spans="5:12" ht="18.75">
+    <row r="477" spans="5:12" ht="18">
       <c r="E477"/>
       <c r="F477"/>
       <c r="G477"/>
@@ -13462,7 +13491,7 @@
       <c r="K477"/>
       <c r="L477"/>
     </row>
-    <row r="478" spans="5:12" ht="18.75">
+    <row r="478" spans="5:12" ht="18">
       <c r="E478"/>
       <c r="F478"/>
       <c r="G478"/>
@@ -13472,7 +13501,7 @@
       <c r="K478"/>
       <c r="L478"/>
     </row>
-    <row r="479" spans="5:12" ht="18.75">
+    <row r="479" spans="5:12" ht="18">
       <c r="E479"/>
       <c r="F479"/>
       <c r="G479"/>
@@ -13482,7 +13511,7 @@
       <c r="K479"/>
       <c r="L479"/>
     </row>
-    <row r="480" spans="5:12" ht="18.75">
+    <row r="480" spans="5:12" ht="18">
       <c r="E480"/>
       <c r="F480"/>
       <c r="G480"/>
@@ -13492,7 +13521,7 @@
       <c r="K480"/>
       <c r="L480"/>
     </row>
-    <row r="481" spans="5:12" ht="18.75">
+    <row r="481" spans="5:12" ht="18">
       <c r="E481"/>
       <c r="F481"/>
       <c r="G481"/>
@@ -13502,7 +13531,7 @@
       <c r="K481"/>
       <c r="L481"/>
     </row>
-    <row r="482" spans="5:12" ht="18.75">
+    <row r="482" spans="5:12" ht="18">
       <c r="E482"/>
       <c r="F482"/>
       <c r="G482"/>
@@ -13512,7 +13541,7 @@
       <c r="K482"/>
       <c r="L482"/>
     </row>
-    <row r="483" spans="5:12" ht="18.75">
+    <row r="483" spans="5:12" ht="18">
       <c r="E483"/>
       <c r="F483"/>
       <c r="G483"/>
@@ -13522,7 +13551,7 @@
       <c r="K483"/>
       <c r="L483"/>
     </row>
-    <row r="484" spans="5:12" ht="18.75">
+    <row r="484" spans="5:12" ht="18">
       <c r="E484"/>
       <c r="F484"/>
       <c r="G484"/>
@@ -13532,7 +13561,7 @@
       <c r="K484"/>
       <c r="L484"/>
     </row>
-    <row r="485" spans="5:12" ht="18.75">
+    <row r="485" spans="5:12" ht="18">
       <c r="E485"/>
       <c r="F485"/>
       <c r="G485"/>
@@ -13542,7 +13571,7 @@
       <c r="K485"/>
       <c r="L485"/>
     </row>
-    <row r="486" spans="5:12" ht="18.75">
+    <row r="486" spans="5:12" ht="18">
       <c r="E486"/>
       <c r="F486"/>
       <c r="G486"/>
@@ -13552,7 +13581,7 @@
       <c r="K486"/>
       <c r="L486"/>
     </row>
-    <row r="487" spans="5:12" ht="18.75">
+    <row r="487" spans="5:12" ht="18">
       <c r="E487"/>
       <c r="F487"/>
       <c r="G487"/>
@@ -13562,7 +13591,7 @@
       <c r="K487"/>
       <c r="L487"/>
     </row>
-    <row r="488" spans="5:12" ht="18.75">
+    <row r="488" spans="5:12" ht="18">
       <c r="E488"/>
       <c r="F488"/>
       <c r="G488"/>
@@ -13572,7 +13601,7 @@
       <c r="K488"/>
       <c r="L488"/>
     </row>
-    <row r="489" spans="5:12" ht="18.75">
+    <row r="489" spans="5:12" ht="18">
       <c r="E489"/>
       <c r="F489"/>
       <c r="G489"/>
@@ -13582,7 +13611,7 @@
       <c r="K489"/>
       <c r="L489"/>
     </row>
-    <row r="490" spans="5:12" ht="18.75">
+    <row r="490" spans="5:12" ht="18">
       <c r="E490"/>
       <c r="F490"/>
       <c r="G490"/>
@@ -13592,7 +13621,7 @@
       <c r="K490"/>
       <c r="L490"/>
     </row>
-    <row r="491" spans="5:12" ht="18.75">
+    <row r="491" spans="5:12" ht="18">
       <c r="E491"/>
       <c r="F491"/>
       <c r="G491"/>
@@ -13602,7 +13631,7 @@
       <c r="K491"/>
       <c r="L491"/>
     </row>
-    <row r="492" spans="5:12" ht="18.75">
+    <row r="492" spans="5:12" ht="18">
       <c r="E492"/>
       <c r="F492"/>
       <c r="G492"/>
@@ -13612,7 +13641,7 @@
       <c r="K492"/>
       <c r="L492"/>
     </row>
-    <row r="493" spans="5:12" ht="18.75">
+    <row r="493" spans="5:12" ht="18">
       <c r="E493"/>
       <c r="F493"/>
       <c r="G493"/>
@@ -13622,7 +13651,7 @@
       <c r="K493"/>
       <c r="L493"/>
     </row>
-    <row r="494" spans="5:12" ht="18.75">
+    <row r="494" spans="5:12" ht="18">
       <c r="E494"/>
       <c r="F494"/>
       <c r="G494"/>
@@ -13632,7 +13661,7 @@
       <c r="K494"/>
       <c r="L494"/>
     </row>
-    <row r="495" spans="5:12" ht="18.75">
+    <row r="495" spans="5:12" ht="18">
       <c r="E495"/>
       <c r="F495"/>
       <c r="G495"/>
@@ -13642,7 +13671,7 @@
       <c r="K495"/>
       <c r="L495"/>
     </row>
-    <row r="496" spans="5:12" ht="18.75">
+    <row r="496" spans="5:12" ht="18">
       <c r="E496"/>
       <c r="F496"/>
       <c r="G496"/>
@@ -13652,7 +13681,7 @@
       <c r="K496"/>
       <c r="L496"/>
     </row>
-    <row r="497" spans="5:12" ht="18.75">
+    <row r="497" spans="5:12" ht="18">
       <c r="E497"/>
       <c r="F497"/>
       <c r="G497"/>
@@ -13662,7 +13691,7 @@
       <c r="K497"/>
       <c r="L497"/>
     </row>
-    <row r="498" spans="5:12" ht="18.75">
+    <row r="498" spans="5:12" ht="18">
       <c r="E498"/>
       <c r="F498"/>
       <c r="G498"/>
@@ -13672,7 +13701,7 @@
       <c r="K498"/>
       <c r="L498"/>
     </row>
-    <row r="499" spans="5:12" ht="18.75">
+    <row r="499" spans="5:12" ht="18">
       <c r="E499"/>
       <c r="F499"/>
       <c r="G499"/>
@@ -13682,7 +13711,7 @@
       <c r="K499"/>
       <c r="L499"/>
     </row>
-    <row r="500" spans="5:12" ht="18.75">
+    <row r="500" spans="5:12" ht="18">
       <c r="E500"/>
       <c r="F500"/>
       <c r="G500"/>
@@ -13692,7 +13721,7 @@
       <c r="K500"/>
       <c r="L500"/>
     </row>
-    <row r="501" spans="5:12" ht="18.75">
+    <row r="501" spans="5:12" ht="18">
       <c r="E501"/>
       <c r="F501"/>
       <c r="G501"/>
@@ -13702,7 +13731,7 @@
       <c r="K501"/>
       <c r="L501"/>
     </row>
-    <row r="502" spans="5:12" ht="18.75">
+    <row r="502" spans="5:12" ht="18">
       <c r="E502"/>
       <c r="F502"/>
       <c r="G502"/>
@@ -13712,7 +13741,7 @@
       <c r="K502"/>
       <c r="L502"/>
     </row>
-    <row r="503" spans="5:12" ht="18.75">
+    <row r="503" spans="5:12" ht="18">
       <c r="E503"/>
       <c r="F503"/>
       <c r="G503"/>
@@ -13722,7 +13751,7 @@
       <c r="K503"/>
       <c r="L503"/>
     </row>
-    <row r="504" spans="5:12" ht="18.75">
+    <row r="504" spans="5:12" ht="18">
       <c r="E504"/>
       <c r="F504"/>
       <c r="G504"/>
@@ -13732,7 +13761,7 @@
       <c r="K504"/>
       <c r="L504"/>
     </row>
-    <row r="505" spans="5:12" ht="18.75">
+    <row r="505" spans="5:12" ht="18">
       <c r="E505"/>
       <c r="F505"/>
       <c r="G505"/>
@@ -13742,7 +13771,7 @@
       <c r="K505"/>
       <c r="L505"/>
     </row>
-    <row r="506" spans="5:12" ht="18.75">
+    <row r="506" spans="5:12" ht="18">
       <c r="E506"/>
       <c r="F506"/>
       <c r="G506"/>
@@ -13752,7 +13781,7 @@
       <c r="K506"/>
       <c r="L506"/>
     </row>
-    <row r="507" spans="5:12" ht="18.75">
+    <row r="507" spans="5:12" ht="18">
       <c r="E507"/>
       <c r="F507"/>
       <c r="G507"/>
@@ -13771,12 +13800,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D1121A1-AAC1-412E-BCE5-349D5BD787B7}">
   <dimension ref="A1:C497"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="63.375" customWidth="1"/>
+    <col min="1" max="1" width="63.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.5">
+    <row r="1" spans="1:3" ht="19.8">
       <c r="A1" s="38" t="s">
         <v>791</v>
       </c>
@@ -13817,7 +13846,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="56.25">
+    <row r="9" spans="1:3" ht="54">
       <c r="A9" t="s">
         <v>127</v>
       </c>
@@ -16280,19 +16309,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{404489B2-A1E2-44FE-B7A5-866F29FE8703}">
   <dimension ref="B2:I13"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="5.375" customWidth="1"/>
-    <col min="3" max="3" width="16.625" customWidth="1"/>
+    <col min="2" max="2" width="5.3984375" customWidth="1"/>
+    <col min="3" max="3" width="16.59765625" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="16.625" customWidth="1"/>
-    <col min="6" max="6" width="21.625" customWidth="1"/>
+    <col min="5" max="5" width="16.59765625" customWidth="1"/>
+    <col min="6" max="6" width="21.59765625" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="13.375" customWidth="1"/>
-    <col min="9" max="9" width="23.375" customWidth="1"/>
+    <col min="8" max="8" width="13.3984375" customWidth="1"/>
+    <col min="9" max="9" width="23.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="19.5">
+    <row r="2" spans="2:9" ht="19.8">
       <c r="B2" s="38" t="s">
         <v>722</v>
       </c>
@@ -16575,16 +16604,16 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{424A1FA2-E78F-432E-B6A2-85174588E0D2}">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="13.375" customWidth="1"/>
+    <col min="2" max="2" width="13.3984375" customWidth="1"/>
     <col min="3" max="3" width="7.5" customWidth="1"/>
-    <col min="4" max="5" width="43.375" customWidth="1"/>
+    <col min="4" max="5" width="43.3984375" customWidth="1"/>
     <col min="6" max="6" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.5">
+    <row r="1" spans="1:6" ht="18.600000000000001">
       <c r="A1" s="31" t="s">
         <v>658</v>
       </c>
@@ -16609,7 +16638,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="56.25">
+    <row r="4" spans="1:6" ht="54">
       <c r="A4" s="34">
         <v>1</v>
       </c>
@@ -16629,7 +16658,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="47.25">
+    <row r="5" spans="1:6" ht="36">
       <c r="A5" s="34">
         <v>2</v>
       </c>
@@ -16649,7 +16678,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="37.5">
+    <row r="6" spans="1:6" ht="36">
       <c r="A6" s="34">
         <v>3</v>
       </c>
@@ -16669,7 +16698,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="56.25">
+    <row r="7" spans="1:6" ht="36">
       <c r="A7" s="34">
         <v>4</v>
       </c>
@@ -16769,7 +16798,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="37.5">
+    <row r="12" spans="1:6" ht="36">
       <c r="A12" s="34">
         <v>9</v>
       </c>
